--- a/data/input/cleansheet.xlsx
+++ b/data/input/cleansheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mckessoncorpca-my.sharepoint.com/personal/masood_ghasemi_mckesson_ca/Documents/LastMile_git/data/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="8_{61DBF404-4647-48BF-959A-B32C5A37762D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E4C4F4E-85F4-45C9-9E0C-3A5D2A2D6A53}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="8_{61DBF404-4647-48BF-959A-B32C5A37762D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10A4D273-845E-4933-B4FF-86811DB7A500}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0BDE470A-3BBA-4A1F-A6D7-67680F331B83}"/>
   </bookViews>
@@ -777,10 +777,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1139,10 +1135,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="3">
-        <v>23.76</v>
+        <v>34.33</v>
       </c>
       <c r="D2" s="6">
-        <v>28.85</v>
+        <v>41.56</v>
       </c>
       <c r="E2">
         <v>2026</v>
@@ -1159,10 +1155,10 @@
         <v>7</v>
       </c>
       <c r="C3" s="3">
-        <v>26.39</v>
+        <v>42.14</v>
       </c>
       <c r="D3" s="6">
-        <v>32.44</v>
+        <v>51.74</v>
       </c>
       <c r="E3">
         <v>2026</v>
@@ -1179,10 +1175,10 @@
         <v>8</v>
       </c>
       <c r="C4" s="3">
-        <v>23.31</v>
+        <v>28.46</v>
       </c>
       <c r="D4" s="6">
-        <v>28.08</v>
+        <v>34.270000000000003</v>
       </c>
       <c r="E4">
         <v>2026</v>
@@ -1199,10 +1195,10 @@
         <v>9</v>
       </c>
       <c r="C5" s="3">
-        <v>14.63</v>
+        <v>14.7</v>
       </c>
       <c r="D5" s="6">
-        <v>18.2</v>
+        <v>18.25</v>
       </c>
       <c r="E5">
         <v>2026</v>
@@ -1219,10 +1215,10 @@
         <v>10</v>
       </c>
       <c r="C6" s="3">
-        <v>37.340000000000003</v>
+        <v>41.39</v>
       </c>
       <c r="D6" s="6">
-        <v>41.9</v>
+        <v>46.52</v>
       </c>
       <c r="E6">
         <v>2026</v>
@@ -1239,10 +1235,10 @@
         <v>11</v>
       </c>
       <c r="C7" s="3">
-        <v>36.1</v>
+        <v>38.1</v>
       </c>
       <c r="D7" s="6">
-        <v>40.03</v>
+        <v>42.26</v>
       </c>
       <c r="E7">
         <v>2026</v>
@@ -1279,10 +1275,10 @@
         <v>13</v>
       </c>
       <c r="C9" s="3">
-        <v>0</v>
+        <v>31.92</v>
       </c>
       <c r="D9" s="6">
-        <v>0</v>
+        <v>37.89</v>
       </c>
       <c r="E9">
         <v>2026</v>
@@ -1299,10 +1295,10 @@
         <v>14</v>
       </c>
       <c r="C10" s="3">
-        <v>19.850000000000001</v>
+        <v>23.75</v>
       </c>
       <c r="D10" s="6">
-        <v>24.31</v>
+        <v>28.99</v>
       </c>
       <c r="E10">
         <v>2026</v>
@@ -1319,10 +1315,10 @@
         <v>15</v>
       </c>
       <c r="C11" s="3">
-        <v>24.82</v>
+        <v>30.49</v>
       </c>
       <c r="D11" s="6">
-        <v>29.72</v>
+        <v>36.56</v>
       </c>
       <c r="E11">
         <v>2026</v>
@@ -1339,10 +1335,10 @@
         <v>16</v>
       </c>
       <c r="C12" s="3">
-        <v>35.200000000000003</v>
+        <v>60.48</v>
       </c>
       <c r="D12" s="6">
-        <v>43.63</v>
+        <v>75.34</v>
       </c>
       <c r="E12">
         <v>2026</v>
@@ -1359,10 +1355,10 @@
         <v>17</v>
       </c>
       <c r="C13" s="3">
-        <v>26.64</v>
+        <v>38.32</v>
       </c>
       <c r="D13" s="6">
-        <v>29.91</v>
+        <v>43.33</v>
       </c>
       <c r="E13">
         <v>2026</v>
@@ -1379,10 +1375,10 @@
         <v>18</v>
       </c>
       <c r="C14" s="3">
-        <v>22.84</v>
+        <v>23.65</v>
       </c>
       <c r="D14" s="6">
-        <v>25.75</v>
+        <v>26.59</v>
       </c>
       <c r="E14">
         <v>2026</v>
@@ -1399,10 +1395,10 @@
         <v>19</v>
       </c>
       <c r="C15" s="3">
-        <v>17.66</v>
+        <v>18.03</v>
       </c>
       <c r="D15" s="6">
-        <v>21.61</v>
+        <v>22.05</v>
       </c>
       <c r="E15">
         <v>2026</v>
@@ -1419,10 +1415,10 @@
         <v>20</v>
       </c>
       <c r="C16" s="3">
-        <v>17.920000000000002</v>
+        <v>18.39</v>
       </c>
       <c r="D16" s="6">
-        <v>22.43</v>
+        <v>22.97</v>
       </c>
       <c r="E16">
         <v>2026</v>
@@ -1439,10 +1435,10 @@
         <v>21</v>
       </c>
       <c r="C17" s="3">
-        <v>12.42</v>
+        <v>12.58</v>
       </c>
       <c r="D17" s="6">
-        <v>15.08</v>
+        <v>15.22</v>
       </c>
       <c r="E17">
         <v>2026</v>
@@ -1459,10 +1455,10 @@
         <v>22</v>
       </c>
       <c r="C18" s="3">
-        <v>33.47</v>
+        <v>35.97</v>
       </c>
       <c r="D18" s="6">
-        <v>36.25</v>
+        <v>38.770000000000003</v>
       </c>
       <c r="E18">
         <v>2026</v>
@@ -1479,10 +1475,10 @@
         <v>23</v>
       </c>
       <c r="C19" s="3">
-        <v>36.659999999999997</v>
+        <v>40.619999999999997</v>
       </c>
       <c r="D19" s="6">
-        <v>39.96</v>
+        <v>43.97</v>
       </c>
       <c r="E19">
         <v>2026</v>
@@ -1499,10 +1495,10 @@
         <v>24</v>
       </c>
       <c r="C20" s="3">
-        <v>38.65</v>
+        <v>40.659999999999997</v>
       </c>
       <c r="D20" s="6">
-        <v>43.34</v>
+        <v>45.61</v>
       </c>
       <c r="E20">
         <v>2026</v>
@@ -1519,10 +1515,10 @@
         <v>25</v>
       </c>
       <c r="C21" s="3">
-        <v>46.82</v>
+        <v>31.28</v>
       </c>
       <c r="D21" s="6">
-        <v>51.14</v>
+        <v>35.6</v>
       </c>
       <c r="E21">
         <v>2026</v>
@@ -1539,10 +1535,10 @@
         <v>26</v>
       </c>
       <c r="C22" s="3">
-        <v>36.28</v>
+        <v>48.15</v>
       </c>
       <c r="D22" s="6">
-        <v>42.69</v>
+        <v>56.58</v>
       </c>
       <c r="E22">
         <v>2026</v>
@@ -1559,10 +1555,10 @@
         <v>27</v>
       </c>
       <c r="C23" s="3">
-        <v>23.25</v>
+        <v>141.87</v>
       </c>
       <c r="D23" s="6">
-        <v>28.33</v>
+        <v>149.88999999999999</v>
       </c>
       <c r="E23">
         <v>2026</v>
@@ -1579,10 +1575,10 @@
         <v>28</v>
       </c>
       <c r="C24" s="3">
-        <v>45.6</v>
+        <v>54.04</v>
       </c>
       <c r="D24" s="6">
-        <v>51.77</v>
+        <v>61.77</v>
       </c>
       <c r="E24">
         <v>2026</v>
@@ -1599,10 +1595,10 @@
         <v>29</v>
       </c>
       <c r="C25" s="3">
-        <v>37.18</v>
+        <v>49.85</v>
       </c>
       <c r="D25" s="6">
-        <v>43.41</v>
+        <v>59.1</v>
       </c>
       <c r="E25">
         <v>2026</v>
@@ -1619,10 +1615,10 @@
         <v>30</v>
       </c>
       <c r="C26" s="3">
-        <v>147.77000000000001</v>
+        <v>156.77000000000001</v>
       </c>
       <c r="D26" s="6">
-        <v>165</v>
+        <v>176.57</v>
       </c>
       <c r="E26">
         <v>2026</v>
@@ -1639,10 +1635,10 @@
         <v>31</v>
       </c>
       <c r="C27" s="3">
-        <v>24.61</v>
+        <v>30.64</v>
       </c>
       <c r="D27" s="6">
-        <v>29.93</v>
+        <v>37.020000000000003</v>
       </c>
       <c r="E27">
         <v>2026</v>
@@ -1659,10 +1655,10 @@
         <v>32</v>
       </c>
       <c r="C28" s="3">
-        <v>26.86</v>
+        <v>29.83</v>
       </c>
       <c r="D28" s="6">
-        <v>33.64</v>
+        <v>37.33</v>
       </c>
       <c r="E28">
         <v>2026</v>
@@ -1679,10 +1675,10 @@
         <v>33</v>
       </c>
       <c r="C29" s="3">
-        <v>40.31</v>
+        <v>44.08</v>
       </c>
       <c r="D29" s="6">
-        <v>47.49</v>
+        <v>52.13</v>
       </c>
       <c r="E29">
         <v>2026</v>
@@ -1699,10 +1695,10 @@
         <v>34</v>
       </c>
       <c r="C30" s="3">
-        <v>59.06</v>
+        <v>63.57</v>
       </c>
       <c r="D30" s="6">
-        <v>67.319999999999993</v>
+        <v>71.84</v>
       </c>
       <c r="E30">
         <v>2026</v>
@@ -1719,10 +1715,10 @@
         <v>35</v>
       </c>
       <c r="C31" s="3">
-        <v>42.37</v>
+        <v>42.32</v>
       </c>
       <c r="D31" s="6">
-        <v>48.55</v>
+        <v>48.54</v>
       </c>
       <c r="E31">
         <v>2026</v>
@@ -1739,10 +1735,10 @@
         <v>36</v>
       </c>
       <c r="C32" s="3">
-        <v>39.06</v>
+        <v>41.42</v>
       </c>
       <c r="D32" s="6">
-        <v>43.83</v>
+        <v>46.5</v>
       </c>
       <c r="E32">
         <v>2026</v>
@@ -1759,10 +1755,10 @@
         <v>37</v>
       </c>
       <c r="C33" s="3">
-        <v>38.049999999999997</v>
+        <v>40.200000000000003</v>
       </c>
       <c r="D33" s="6">
-        <v>42.34</v>
+        <v>44.78</v>
       </c>
       <c r="E33">
         <v>2026</v>
@@ -1779,10 +1775,10 @@
         <v>38</v>
       </c>
       <c r="C34" s="3">
-        <v>44.44</v>
+        <v>44.73</v>
       </c>
       <c r="D34" s="6">
-        <v>49.19</v>
+        <v>49.54</v>
       </c>
       <c r="E34">
         <v>2026</v>
@@ -1799,10 +1795,10 @@
         <v>39</v>
       </c>
       <c r="C35" s="3">
-        <v>20.64</v>
+        <v>29.18</v>
       </c>
       <c r="D35" s="6">
-        <v>25.02</v>
+        <v>35.26</v>
       </c>
       <c r="E35">
         <v>2026</v>
@@ -1819,10 +1815,10 @@
         <v>40</v>
       </c>
       <c r="C36" s="3">
-        <v>30.74</v>
+        <v>46.33</v>
       </c>
       <c r="D36" s="6">
-        <v>35.44</v>
+        <v>53.12</v>
       </c>
       <c r="E36">
         <v>2026</v>
@@ -1839,10 +1835,10 @@
         <v>41</v>
       </c>
       <c r="C37" s="3">
-        <v>27.83</v>
+        <v>25.55</v>
       </c>
       <c r="D37" s="6">
-        <v>31.96</v>
+        <v>29.44</v>
       </c>
       <c r="E37">
         <v>2026</v>
@@ -1859,10 +1855,10 @@
         <v>42</v>
       </c>
       <c r="C38" s="3">
-        <v>14.16</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="D38" s="6">
-        <v>17.829999999999998</v>
+        <v>25.07</v>
       </c>
       <c r="E38">
         <v>2026</v>
@@ -1879,10 +1875,10 @@
         <v>43</v>
       </c>
       <c r="C39" s="3">
-        <v>18.53</v>
+        <v>21.21</v>
       </c>
       <c r="D39" s="6">
-        <v>23.63</v>
+        <v>27.04</v>
       </c>
       <c r="E39">
         <v>2026</v>
@@ -1899,10 +1895,10 @@
         <v>44</v>
       </c>
       <c r="C40" s="3">
-        <v>24.53</v>
+        <v>37.020000000000003</v>
       </c>
       <c r="D40" s="6">
-        <v>30.56</v>
+        <v>46.08</v>
       </c>
       <c r="E40">
         <v>2026</v>
@@ -1919,10 +1915,10 @@
         <v>45</v>
       </c>
       <c r="C41" s="3">
-        <v>71.930000000000007</v>
+        <v>70.5</v>
       </c>
       <c r="D41" s="6">
-        <v>75.680000000000007</v>
+        <v>75.010000000000005</v>
       </c>
       <c r="E41">
         <v>2026</v>
@@ -1939,10 +1935,10 @@
         <v>46</v>
       </c>
       <c r="C42" s="3">
-        <v>19.809999999999999</v>
+        <v>35.950000000000003</v>
       </c>
       <c r="D42" s="6">
-        <v>24.53</v>
+        <v>44.38</v>
       </c>
       <c r="E42">
         <v>2026</v>
@@ -1959,10 +1955,10 @@
         <v>47</v>
       </c>
       <c r="C43" s="3">
-        <v>22.42</v>
+        <v>21.13</v>
       </c>
       <c r="D43" s="6">
-        <v>25.79</v>
+        <v>24.33</v>
       </c>
       <c r="E43">
         <v>2026</v>
@@ -1979,10 +1975,10 @@
         <v>48</v>
       </c>
       <c r="C44" s="3">
-        <v>31.74</v>
+        <v>39.03</v>
       </c>
       <c r="D44" s="6">
-        <v>38.96</v>
+        <v>48.15</v>
       </c>
       <c r="E44">
         <v>2026</v>
@@ -1999,10 +1995,10 @@
         <v>49</v>
       </c>
       <c r="C45" s="3">
-        <v>25.59</v>
+        <v>28.02</v>
       </c>
       <c r="D45" s="6">
-        <v>32.47</v>
+        <v>35.51</v>
       </c>
       <c r="E45">
         <v>2026</v>
@@ -2019,10 +2015,10 @@
         <v>50</v>
       </c>
       <c r="C46" s="3">
-        <v>26.08</v>
+        <v>26.31</v>
       </c>
       <c r="D46" s="6">
-        <v>33.15</v>
+        <v>33.369999999999997</v>
       </c>
       <c r="E46">
         <v>2026</v>
@@ -2039,10 +2035,10 @@
         <v>51</v>
       </c>
       <c r="C47" s="3">
-        <v>15.12</v>
+        <v>15.28</v>
       </c>
       <c r="D47" s="6">
-        <v>19.12</v>
+        <v>19.3</v>
       </c>
       <c r="E47">
         <v>2026</v>
@@ -2059,10 +2055,10 @@
         <v>52</v>
       </c>
       <c r="C48" s="3">
-        <v>25.81</v>
+        <v>34.61</v>
       </c>
       <c r="D48" s="6">
-        <v>31.01</v>
+        <v>41.4</v>
       </c>
       <c r="E48">
         <v>2026</v>
@@ -2079,10 +2075,10 @@
         <v>53</v>
       </c>
       <c r="C49" s="3">
-        <v>17.98</v>
+        <v>29.26</v>
       </c>
       <c r="D49" s="6">
-        <v>22.58</v>
+        <v>36.700000000000003</v>
       </c>
       <c r="E49">
         <v>2026</v>
@@ -2099,10 +2095,10 @@
         <v>54</v>
       </c>
       <c r="C50" s="3">
-        <v>39.049999999999997</v>
+        <v>37.76</v>
       </c>
       <c r="D50" s="6">
-        <v>43.48</v>
+        <v>42.16</v>
       </c>
       <c r="E50">
         <v>2026</v>
@@ -2119,10 +2115,10 @@
         <v>55</v>
       </c>
       <c r="C51" s="3">
-        <v>46.75</v>
+        <v>35.15</v>
       </c>
       <c r="D51" s="6">
-        <v>52.98</v>
+        <v>39.950000000000003</v>
       </c>
       <c r="E51">
         <v>2026</v>
@@ -2139,10 +2135,10 @@
         <v>56</v>
       </c>
       <c r="C52" s="3">
-        <v>51.34</v>
+        <v>55.11</v>
       </c>
       <c r="D52" s="6">
-        <v>55.54</v>
+        <v>59.46</v>
       </c>
       <c r="E52">
         <v>2026</v>
@@ -2159,10 +2155,10 @@
         <v>57</v>
       </c>
       <c r="C53" s="3">
-        <v>40.29</v>
+        <v>56.25</v>
       </c>
       <c r="D53" s="6">
-        <v>47.18</v>
+        <v>67.63</v>
       </c>
       <c r="E53">
         <v>2026</v>
@@ -2179,10 +2175,10 @@
         <v>58</v>
       </c>
       <c r="C54" s="3">
-        <v>32.520000000000003</v>
+        <v>40.53</v>
       </c>
       <c r="D54" s="6">
-        <v>38.33</v>
+        <v>48.05</v>
       </c>
       <c r="E54">
         <v>2026</v>
@@ -2199,10 +2195,10 @@
         <v>59</v>
       </c>
       <c r="C55" s="3">
-        <v>38.979999999999997</v>
+        <v>42.15</v>
       </c>
       <c r="D55" s="6">
-        <v>43.45</v>
+        <v>47.5</v>
       </c>
       <c r="E55">
         <v>2026</v>
@@ -2219,10 +2215,10 @@
         <v>60</v>
       </c>
       <c r="C56" s="3">
-        <v>35.01</v>
+        <v>35.299999999999997</v>
       </c>
       <c r="D56" s="6">
-        <v>38.11</v>
+        <v>38.35</v>
       </c>
       <c r="E56">
         <v>2026</v>
@@ -2239,10 +2235,10 @@
         <v>61</v>
       </c>
       <c r="C57" s="3">
-        <v>14.22</v>
+        <v>31.93</v>
       </c>
       <c r="D57" s="6">
-        <v>17.91</v>
+        <v>40.020000000000003</v>
       </c>
       <c r="E57">
         <v>2026</v>
@@ -2259,10 +2255,10 @@
         <v>62</v>
       </c>
       <c r="C58" s="3">
-        <v>15.1</v>
+        <v>31.98</v>
       </c>
       <c r="D58" s="6">
-        <v>18.77</v>
+        <v>39.619999999999997</v>
       </c>
       <c r="E58">
         <v>2026</v>
@@ -2279,10 +2275,10 @@
         <v>63</v>
       </c>
       <c r="C59" s="3">
-        <v>14.37</v>
+        <v>26.28</v>
       </c>
       <c r="D59" s="6">
-        <v>18.14</v>
+        <v>33.119999999999997</v>
       </c>
       <c r="E59">
         <v>2026</v>
@@ -2299,10 +2295,10 @@
         <v>64</v>
       </c>
       <c r="C60" s="3">
-        <v>12.39</v>
+        <v>26.57</v>
       </c>
       <c r="D60" s="6">
-        <v>15.59</v>
+        <v>33.35</v>
       </c>
       <c r="E60">
         <v>2026</v>
@@ -2319,10 +2315,10 @@
         <v>65</v>
       </c>
       <c r="C61" s="3">
-        <v>20.81</v>
+        <v>34.04</v>
       </c>
       <c r="D61" s="6">
-        <v>25.55</v>
+        <v>41.66</v>
       </c>
       <c r="E61">
         <v>2026</v>
@@ -2339,10 +2335,10 @@
         <v>66</v>
       </c>
       <c r="C62" s="3">
-        <v>24.13</v>
+        <v>25.96</v>
       </c>
       <c r="D62" s="6">
-        <v>30.64</v>
+        <v>32.92</v>
       </c>
       <c r="E62">
         <v>2026</v>
@@ -2359,10 +2355,10 @@
         <v>67</v>
       </c>
       <c r="C63" s="3">
-        <v>16.059999999999999</v>
+        <v>24.39</v>
       </c>
       <c r="D63" s="6">
-        <v>20.09</v>
+        <v>30.46</v>
       </c>
       <c r="E63">
         <v>2026</v>
@@ -2379,10 +2375,10 @@
         <v>68</v>
       </c>
       <c r="C64" s="3">
-        <v>15.09</v>
+        <v>18.5</v>
       </c>
       <c r="D64" s="6">
-        <v>19.18</v>
+        <v>23.51</v>
       </c>
       <c r="E64">
         <v>2026</v>
@@ -2399,10 +2395,10 @@
         <v>69</v>
       </c>
       <c r="C65" s="3">
-        <v>18.62</v>
+        <v>25.51</v>
       </c>
       <c r="D65" s="6">
-        <v>22.93</v>
+        <v>31.27</v>
       </c>
       <c r="E65">
         <v>2026</v>
@@ -2419,10 +2415,10 @@
         <v>70</v>
       </c>
       <c r="C66" s="3">
-        <v>20.51</v>
+        <v>29.5</v>
       </c>
       <c r="D66" s="6">
-        <v>25.25</v>
+        <v>36.229999999999997</v>
       </c>
       <c r="E66">
         <v>2026</v>
@@ -2439,10 +2435,10 @@
         <v>71</v>
       </c>
       <c r="C67" s="3">
-        <v>17.489999999999998</v>
+        <v>22.16</v>
       </c>
       <c r="D67" s="6">
-        <v>21.63</v>
+        <v>27.3</v>
       </c>
       <c r="E67">
         <v>2026</v>
@@ -2459,10 +2455,10 @@
         <v>72</v>
       </c>
       <c r="C68" s="3">
-        <v>24.09</v>
+        <v>28.38</v>
       </c>
       <c r="D68" s="6">
-        <v>28.99</v>
+        <v>34.24</v>
       </c>
       <c r="E68">
         <v>2026</v>
@@ -2479,10 +2475,10 @@
         <v>73</v>
       </c>
       <c r="C69" s="3">
-        <v>27.77</v>
+        <v>40.08</v>
       </c>
       <c r="D69" s="6">
-        <v>32.69</v>
+        <v>46.98</v>
       </c>
       <c r="E69">
         <v>2026</v>
@@ -2499,10 +2495,10 @@
         <v>74</v>
       </c>
       <c r="C70" s="3">
-        <v>29.33</v>
+        <v>35.049999999999997</v>
       </c>
       <c r="D70" s="6">
-        <v>36.619999999999997</v>
+        <v>43.64</v>
       </c>
       <c r="E70">
         <v>2026</v>
@@ -2519,10 +2515,10 @@
         <v>75</v>
       </c>
       <c r="C71" s="3">
-        <v>25.97</v>
+        <v>30.35</v>
       </c>
       <c r="D71" s="6">
-        <v>31.15</v>
+        <v>36.22</v>
       </c>
       <c r="E71">
         <v>2026</v>
@@ -2539,10 +2535,10 @@
         <v>76</v>
       </c>
       <c r="C72" s="3">
-        <v>17.16</v>
+        <v>28.09</v>
       </c>
       <c r="D72" s="6">
-        <v>21.57</v>
+        <v>35.229999999999997</v>
       </c>
       <c r="E72">
         <v>2026</v>
@@ -2559,10 +2555,10 @@
         <v>77</v>
       </c>
       <c r="C73" s="3">
-        <v>26.61</v>
+        <v>37.119999999999997</v>
       </c>
       <c r="D73" s="6">
-        <v>33.32</v>
+        <v>46.31</v>
       </c>
       <c r="E73">
         <v>2026</v>
@@ -2579,10 +2575,10 @@
         <v>78</v>
       </c>
       <c r="C74" s="3">
-        <v>26.05</v>
+        <v>31.64</v>
       </c>
       <c r="D74" s="6">
-        <v>32.22</v>
+        <v>38.89</v>
       </c>
       <c r="E74">
         <v>2026</v>
@@ -2599,10 +2595,10 @@
         <v>79</v>
       </c>
       <c r="C75" s="3">
-        <v>21.19</v>
+        <v>24.87</v>
       </c>
       <c r="D75" s="6">
-        <v>26.02</v>
+        <v>30.45</v>
       </c>
       <c r="E75">
         <v>2026</v>
@@ -2619,10 +2615,10 @@
         <v>80</v>
       </c>
       <c r="C76" s="3">
-        <v>28.22</v>
+        <v>37.450000000000003</v>
       </c>
       <c r="D76" s="6">
-        <v>35.04</v>
+        <v>46.35</v>
       </c>
       <c r="E76">
         <v>2026</v>
@@ -2639,10 +2635,10 @@
         <v>81</v>
       </c>
       <c r="C77" s="3">
-        <v>20.02</v>
+        <v>26.77</v>
       </c>
       <c r="D77" s="6">
-        <v>24.63</v>
+        <v>32.78</v>
       </c>
       <c r="E77">
         <v>2026</v>
@@ -2659,10 +2655,10 @@
         <v>82</v>
       </c>
       <c r="C78" s="3">
-        <v>28.07</v>
+        <v>29.9</v>
       </c>
       <c r="D78" s="6">
-        <v>34.99</v>
+        <v>37.130000000000003</v>
       </c>
       <c r="E78">
         <v>2026</v>
@@ -2679,10 +2675,10 @@
         <v>83</v>
       </c>
       <c r="C79" s="3">
-        <v>30.75</v>
+        <v>58.38</v>
       </c>
       <c r="D79" s="6">
-        <v>37.72</v>
+        <v>71.37</v>
       </c>
       <c r="E79">
         <v>2026</v>
@@ -2699,10 +2695,10 @@
         <v>84</v>
       </c>
       <c r="C80" s="3">
-        <v>16.32</v>
+        <v>24.37</v>
       </c>
       <c r="D80" s="6">
-        <v>20.03</v>
+        <v>29.8</v>
       </c>
       <c r="E80">
         <v>2026</v>
@@ -2719,10 +2715,10 @@
         <v>85</v>
       </c>
       <c r="C81" s="3">
-        <v>19.29</v>
+        <v>25.51</v>
       </c>
       <c r="D81" s="6">
-        <v>24.35</v>
+        <v>32.14</v>
       </c>
       <c r="E81">
         <v>2026</v>
@@ -2739,10 +2735,10 @@
         <v>86</v>
       </c>
       <c r="C82" s="3">
-        <v>18.14</v>
+        <v>28.97</v>
       </c>
       <c r="D82" s="6">
-        <v>22.37</v>
+        <v>35.590000000000003</v>
       </c>
       <c r="E82">
         <v>2026</v>
@@ -2759,10 +2755,10 @@
         <v>87</v>
       </c>
       <c r="C83" s="3">
-        <v>34.82</v>
+        <v>31.7</v>
       </c>
       <c r="D83" s="6">
-        <v>39.26</v>
+        <v>36.11</v>
       </c>
       <c r="E83">
         <v>2026</v>
@@ -2779,10 +2775,10 @@
         <v>88</v>
       </c>
       <c r="C84" s="3">
-        <v>46.6</v>
+        <v>44.48</v>
       </c>
       <c r="D84" s="6">
-        <v>50.61</v>
+        <v>48.47</v>
       </c>
       <c r="E84">
         <v>2026</v>
@@ -2799,10 +2795,10 @@
         <v>89</v>
       </c>
       <c r="C85" s="3">
-        <v>40.020000000000003</v>
+        <v>39.409999999999997</v>
       </c>
       <c r="D85" s="6">
-        <v>44.29</v>
+        <v>43.84</v>
       </c>
       <c r="E85">
         <v>2026</v>
@@ -2819,10 +2815,10 @@
         <v>90</v>
       </c>
       <c r="C86" s="3">
-        <v>26.99</v>
+        <v>25.94</v>
       </c>
       <c r="D86" s="6">
-        <v>31.75</v>
+        <v>30.78</v>
       </c>
       <c r="E86">
         <v>2026</v>
@@ -2839,10 +2835,10 @@
         <v>91</v>
       </c>
       <c r="C87" s="3">
-        <v>38.24</v>
+        <v>36.42</v>
       </c>
       <c r="D87" s="6">
-        <v>42.53</v>
+        <v>40.65</v>
       </c>
       <c r="E87">
         <v>2026</v>
@@ -2859,10 +2855,10 @@
         <v>92</v>
       </c>
       <c r="C88" s="3">
-        <v>36.29</v>
+        <v>34.93</v>
       </c>
       <c r="D88" s="6">
-        <v>41.77</v>
+        <v>40.29</v>
       </c>
       <c r="E88">
         <v>2026</v>
@@ -2879,10 +2875,10 @@
         <v>93</v>
       </c>
       <c r="C89" s="3">
-        <v>28.85</v>
+        <v>38.72</v>
       </c>
       <c r="D89" s="6">
-        <v>34.47</v>
+        <v>45.95</v>
       </c>
       <c r="E89">
         <v>2026</v>
@@ -2899,10 +2895,10 @@
         <v>94</v>
       </c>
       <c r="C90" s="3">
-        <v>28.36</v>
+        <v>35.69</v>
       </c>
       <c r="D90" s="6">
-        <v>35.67</v>
+        <v>44.82</v>
       </c>
       <c r="E90">
         <v>2026</v>
@@ -2919,10 +2915,10 @@
         <v>95</v>
       </c>
       <c r="C91" s="3">
-        <v>33.83</v>
+        <v>47.42</v>
       </c>
       <c r="D91" s="6">
-        <v>41.04</v>
+        <v>57.3</v>
       </c>
       <c r="E91">
         <v>2026</v>
@@ -2939,10 +2935,10 @@
         <v>96</v>
       </c>
       <c r="C92" s="3">
-        <v>31.63</v>
+        <v>44.42</v>
       </c>
       <c r="D92" s="6">
-        <v>38.46</v>
+        <v>53.82</v>
       </c>
       <c r="E92">
         <v>2026</v>
@@ -2959,10 +2955,10 @@
         <v>97</v>
       </c>
       <c r="C93" s="3">
-        <v>64.67</v>
+        <v>70.849999999999994</v>
       </c>
       <c r="D93" s="6">
-        <v>72.34</v>
+        <v>79.209999999999994</v>
       </c>
       <c r="E93">
         <v>2026</v>
@@ -2979,10 +2975,10 @@
         <v>98</v>
       </c>
       <c r="C94" s="3">
-        <v>32.97</v>
+        <v>44.84</v>
       </c>
       <c r="D94" s="6">
-        <v>38.93</v>
+        <v>52.67</v>
       </c>
       <c r="E94">
         <v>2026</v>
@@ -2999,10 +2995,10 @@
         <v>99</v>
       </c>
       <c r="C95" s="3">
-        <v>48.52</v>
+        <v>54.4</v>
       </c>
       <c r="D95" s="6">
-        <v>53.72</v>
+        <v>60.05</v>
       </c>
       <c r="E95">
         <v>2026</v>
@@ -3019,10 +3015,10 @@
         <v>100</v>
       </c>
       <c r="C96" s="3">
-        <v>64.67</v>
+        <v>69.069999999999993</v>
       </c>
       <c r="D96" s="6">
-        <v>71.53</v>
+        <v>76.36</v>
       </c>
       <c r="E96">
         <v>2026</v>
@@ -3039,10 +3035,10 @@
         <v>101</v>
       </c>
       <c r="C97" s="3">
-        <v>30.79</v>
+        <v>33.67</v>
       </c>
       <c r="D97" s="6">
-        <v>36.79</v>
+        <v>39.96</v>
       </c>
       <c r="E97">
         <v>2026</v>
@@ -3059,10 +3055,10 @@
         <v>102</v>
       </c>
       <c r="C98" s="3">
-        <v>17.41</v>
+        <v>19.68</v>
       </c>
       <c r="D98" s="6">
-        <v>21.37</v>
+        <v>24.07</v>
       </c>
       <c r="E98">
         <v>2026</v>
@@ -3079,10 +3075,10 @@
         <v>103</v>
       </c>
       <c r="C99" s="3">
-        <v>51.61</v>
+        <v>52.59</v>
       </c>
       <c r="D99" s="6">
-        <v>56.95</v>
+        <v>58.01</v>
       </c>
       <c r="E99">
         <v>2026</v>
@@ -3099,10 +3095,10 @@
         <v>104</v>
       </c>
       <c r="C100" s="3">
-        <v>41.89</v>
+        <v>46.3</v>
       </c>
       <c r="D100" s="6">
-        <v>46.03</v>
+        <v>50.85</v>
       </c>
       <c r="E100">
         <v>2026</v>
@@ -3119,10 +3115,10 @@
         <v>105</v>
       </c>
       <c r="C101" s="3">
-        <v>46.29</v>
+        <v>49.41</v>
       </c>
       <c r="D101" s="6">
-        <v>50.88</v>
+        <v>54.5</v>
       </c>
       <c r="E101">
         <v>2026</v>
@@ -3139,10 +3135,10 @@
         <v>106</v>
       </c>
       <c r="C102" s="3">
-        <v>243.69</v>
+        <v>268.79000000000002</v>
       </c>
       <c r="D102" s="6">
-        <v>282.92</v>
+        <v>309.93</v>
       </c>
       <c r="E102">
         <v>2026</v>
@@ -3159,10 +3155,10 @@
         <v>107</v>
       </c>
       <c r="C103" s="3">
-        <v>22.07</v>
+        <v>30</v>
       </c>
       <c r="D103" s="6">
-        <v>28</v>
+        <v>38.090000000000003</v>
       </c>
       <c r="E103">
         <v>2026</v>
@@ -3179,10 +3175,10 @@
         <v>108</v>
       </c>
       <c r="C104" s="3">
-        <v>36.869999999999997</v>
+        <v>32.04</v>
       </c>
       <c r="D104" s="6">
-        <v>42.02</v>
+        <v>37.33</v>
       </c>
       <c r="E104">
         <v>2026</v>
@@ -3199,10 +3195,10 @@
         <v>109</v>
       </c>
       <c r="C105" s="3">
-        <v>50.26</v>
+        <v>54.15</v>
       </c>
       <c r="D105" s="6">
-        <v>55.33</v>
+        <v>59.44</v>
       </c>
       <c r="E105">
         <v>2026</v>
@@ -3219,10 +3215,10 @@
         <v>110</v>
       </c>
       <c r="C106" s="3">
-        <v>44.19</v>
+        <v>60.76</v>
       </c>
       <c r="D106" s="6">
-        <v>50.62</v>
+        <v>69.39</v>
       </c>
       <c r="E106">
         <v>2026</v>
@@ -3239,10 +3235,10 @@
         <v>111</v>
       </c>
       <c r="C107" s="3">
-        <v>48.64</v>
+        <v>49.76</v>
       </c>
       <c r="D107" s="6">
-        <v>54.4</v>
+        <v>55.52</v>
       </c>
       <c r="E107">
         <v>2026</v>
@@ -3259,10 +3255,10 @@
         <v>112</v>
       </c>
       <c r="C108" s="3">
-        <v>141.9</v>
+        <v>141.82</v>
       </c>
       <c r="D108" s="6">
-        <v>180.62</v>
+        <v>180.53</v>
       </c>
       <c r="E108">
         <v>2026</v>
@@ -3279,10 +3275,10 @@
         <v>113</v>
       </c>
       <c r="C109" s="3">
-        <v>46.57</v>
+        <v>89.68</v>
       </c>
       <c r="D109" s="6">
-        <v>53.71</v>
+        <v>97.88</v>
       </c>
       <c r="E109">
         <v>2026</v>
@@ -3299,10 +3295,10 @@
         <v>114</v>
       </c>
       <c r="C110" s="3">
-        <v>67.7</v>
+        <v>74.22</v>
       </c>
       <c r="D110" s="6">
-        <v>75.77</v>
+        <v>82.52</v>
       </c>
       <c r="E110">
         <v>2026</v>
@@ -3319,10 +3315,10 @@
         <v>115</v>
       </c>
       <c r="C111" s="3">
-        <v>45.38</v>
+        <v>60.34</v>
       </c>
       <c r="D111" s="6">
-        <v>54.7</v>
+        <v>73.16</v>
       </c>
       <c r="E111">
         <v>2026</v>
@@ -3339,10 +3335,10 @@
         <v>116</v>
       </c>
       <c r="C112" s="3">
-        <v>29.36</v>
+        <v>29.35</v>
       </c>
       <c r="D112" s="6">
-        <v>33.21</v>
+        <v>33.39</v>
       </c>
       <c r="E112">
         <v>2026</v>
@@ -3359,10 +3355,10 @@
         <v>117</v>
       </c>
       <c r="C113" s="3">
-        <v>43.12</v>
+        <v>51.77</v>
       </c>
       <c r="D113" s="6">
-        <v>52.51</v>
+        <v>63.5</v>
       </c>
       <c r="E113">
         <v>2026</v>
@@ -3379,10 +3375,10 @@
         <v>118</v>
       </c>
       <c r="C114" s="3">
-        <v>64.349999999999994</v>
+        <v>68.430000000000007</v>
       </c>
       <c r="D114" s="6">
-        <v>70.459999999999994</v>
+        <v>74.95</v>
       </c>
       <c r="E114">
         <v>2026</v>
@@ -3399,10 +3395,10 @@
         <v>119</v>
       </c>
       <c r="C115" s="3">
-        <v>28.07</v>
+        <v>26.68</v>
       </c>
       <c r="D115" s="6">
-        <v>31.67</v>
+        <v>30.3</v>
       </c>
       <c r="E115">
         <v>2026</v>
@@ -3419,10 +3415,10 @@
         <v>120</v>
       </c>
       <c r="C116" s="3">
-        <v>32.869999999999997</v>
+        <v>32.700000000000003</v>
       </c>
       <c r="D116" s="6">
-        <v>36.33</v>
+        <v>36.31</v>
       </c>
       <c r="E116">
         <v>2026</v>
@@ -3439,10 +3435,10 @@
         <v>121</v>
       </c>
       <c r="C117" s="3">
-        <v>32.22</v>
+        <v>33.049999999999997</v>
       </c>
       <c r="D117" s="6">
-        <v>35.39</v>
+        <v>36.47</v>
       </c>
       <c r="E117">
         <v>2026</v>
@@ -3459,10 +3455,10 @@
         <v>122</v>
       </c>
       <c r="C118" s="3">
-        <v>54.24</v>
+        <v>58.08</v>
       </c>
       <c r="D118" s="6">
-        <v>60.92</v>
+        <v>66.150000000000006</v>
       </c>
       <c r="E118">
         <v>2026</v>
@@ -3479,10 +3475,10 @@
         <v>123</v>
       </c>
       <c r="C119" s="3">
-        <v>37.25</v>
+        <v>36.17</v>
       </c>
       <c r="D119" s="6">
-        <v>40.44</v>
+        <v>39.369999999999997</v>
       </c>
       <c r="E119">
         <v>2026</v>
@@ -3499,10 +3495,10 @@
         <v>124</v>
       </c>
       <c r="C120" s="3">
-        <v>101.53</v>
+        <v>104.33</v>
       </c>
       <c r="D120" s="6">
-        <v>106.7</v>
+        <v>110.64</v>
       </c>
       <c r="E120">
         <v>2026</v>
@@ -3519,10 +3515,10 @@
         <v>125</v>
       </c>
       <c r="C121" s="3">
-        <v>17.739999999999998</v>
+        <v>24.09</v>
       </c>
       <c r="D121" s="6">
-        <v>21.94</v>
+        <v>29.65</v>
       </c>
       <c r="E121">
         <v>2026</v>
@@ -3539,10 +3535,10 @@
         <v>126</v>
       </c>
       <c r="C122" s="3">
-        <v>18.14</v>
+        <v>24</v>
       </c>
       <c r="D122" s="6">
-        <v>22.24</v>
+        <v>29.4</v>
       </c>
       <c r="E122">
         <v>2026</v>
@@ -3559,10 +3555,10 @@
         <v>127</v>
       </c>
       <c r="C123" s="3">
-        <v>19.23</v>
+        <v>27.46</v>
       </c>
       <c r="D123" s="6">
-        <v>23.72</v>
+        <v>33.86</v>
       </c>
       <c r="E123">
         <v>2026</v>
@@ -3579,10 +3575,10 @@
         <v>128</v>
       </c>
       <c r="C124" s="3">
-        <v>22.2</v>
+        <v>28.75</v>
       </c>
       <c r="D124" s="6">
-        <v>27.08</v>
+        <v>34.94</v>
       </c>
       <c r="E124">
         <v>2026</v>
@@ -3599,10 +3595,10 @@
         <v>129</v>
       </c>
       <c r="C125" s="3">
-        <v>38.450000000000003</v>
+        <v>43.19</v>
       </c>
       <c r="D125" s="6">
-        <v>45.2</v>
+        <v>50.48</v>
       </c>
       <c r="E125">
         <v>2026</v>
@@ -3619,10 +3615,10 @@
         <v>130</v>
       </c>
       <c r="C126" s="3">
-        <v>25.7</v>
+        <v>37.65</v>
       </c>
       <c r="D126" s="6">
-        <v>30.96</v>
+        <v>45.45</v>
       </c>
       <c r="E126">
         <v>2026</v>
@@ -3639,10 +3635,10 @@
         <v>131</v>
       </c>
       <c r="C127" s="3">
-        <v>22.63</v>
+        <v>31.92</v>
       </c>
       <c r="D127" s="6">
-        <v>27.34</v>
+        <v>38.44</v>
       </c>
       <c r="E127">
         <v>2026</v>
@@ -3659,10 +3655,10 @@
         <v>132</v>
       </c>
       <c r="C128" s="3">
-        <v>30.12</v>
+        <v>35.79</v>
       </c>
       <c r="D128" s="6">
-        <v>35.770000000000003</v>
+        <v>42.5</v>
       </c>
       <c r="E128">
         <v>2026</v>
@@ -3679,10 +3675,10 @@
         <v>133</v>
       </c>
       <c r="C129" s="3">
-        <v>22.09</v>
+        <v>29.5</v>
       </c>
       <c r="D129" s="6">
-        <v>27.26</v>
+        <v>36.24</v>
       </c>
       <c r="E129">
         <v>2026</v>
@@ -3699,10 +3695,10 @@
         <v>134</v>
       </c>
       <c r="C130" s="3">
-        <v>5.74</v>
+        <v>53.73</v>
       </c>
       <c r="D130" s="6">
-        <v>7.32</v>
+        <v>68.489999999999995</v>
       </c>
       <c r="E130">
         <v>2026</v>
@@ -3719,10 +3715,10 @@
         <v>135</v>
       </c>
       <c r="C131" s="3">
-        <v>31.09</v>
+        <v>40.64</v>
       </c>
       <c r="D131" s="6">
-        <v>36.909999999999997</v>
+        <v>47.57</v>
       </c>
       <c r="E131">
         <v>2026</v>
@@ -3739,10 +3735,10 @@
         <v>136</v>
       </c>
       <c r="C132" s="3">
-        <v>20.41</v>
+        <v>31.35</v>
       </c>
       <c r="D132" s="6">
-        <v>25.4</v>
+        <v>38.700000000000003</v>
       </c>
       <c r="E132">
         <v>2026</v>
@@ -3759,10 +3755,10 @@
         <v>137</v>
       </c>
       <c r="C133" s="3">
-        <v>66.209999999999994</v>
+        <v>69.48</v>
       </c>
       <c r="D133" s="6">
-        <v>71.680000000000007</v>
+        <v>75.47</v>
       </c>
       <c r="E133">
         <v>2026</v>
@@ -3779,10 +3775,10 @@
         <v>138</v>
       </c>
       <c r="C134" s="3">
-        <v>33.51</v>
+        <v>37.229999999999997</v>
       </c>
       <c r="D134" s="6">
-        <v>37.69</v>
+        <v>42.15</v>
       </c>
       <c r="E134">
         <v>2026</v>
@@ -3799,10 +3795,10 @@
         <v>139</v>
       </c>
       <c r="C135" s="3">
-        <v>35.020000000000003</v>
+        <v>42.59</v>
       </c>
       <c r="D135" s="6">
-        <v>41.07</v>
+        <v>49.71</v>
       </c>
       <c r="E135">
         <v>2026</v>
@@ -3819,10 +3815,10 @@
         <v>140</v>
       </c>
       <c r="C136" s="3">
-        <v>13.96</v>
+        <v>15.67</v>
       </c>
       <c r="D136" s="6">
-        <v>17.18</v>
+        <v>19.309999999999999</v>
       </c>
       <c r="E136">
         <v>2026</v>
@@ -3839,10 +3835,10 @@
         <v>141</v>
       </c>
       <c r="C137" s="3">
-        <v>13.22</v>
+        <v>16.34</v>
       </c>
       <c r="D137" s="6">
-        <v>15.89</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="E137">
         <v>2026</v>
@@ -3859,10 +3855,10 @@
         <v>142</v>
       </c>
       <c r="C138" s="3">
-        <v>22.3</v>
+        <v>33.82</v>
       </c>
       <c r="D138" s="6">
-        <v>27.85</v>
+        <v>41.97</v>
       </c>
       <c r="E138">
         <v>2026</v>
@@ -3879,10 +3875,10 @@
         <v>143</v>
       </c>
       <c r="C139" s="3">
-        <v>29.7</v>
+        <v>47.17</v>
       </c>
       <c r="D139" s="6">
-        <v>37.86</v>
+        <v>60.09</v>
       </c>
       <c r="E139">
         <v>2026</v>
@@ -3899,10 +3895,10 @@
         <v>144</v>
       </c>
       <c r="C140" s="3">
-        <v>14.76</v>
+        <v>33.729999999999997</v>
       </c>
       <c r="D140" s="6">
-        <v>18.36</v>
+        <v>42.02</v>
       </c>
       <c r="E140">
         <v>2026</v>
@@ -3919,10 +3915,10 @@
         <v>145</v>
       </c>
       <c r="C141" s="3">
-        <v>21.06</v>
+        <v>37.520000000000003</v>
       </c>
       <c r="D141" s="6">
-        <v>26.19</v>
+        <v>46.6</v>
       </c>
       <c r="E141">
         <v>2026</v>
@@ -3939,10 +3935,10 @@
         <v>146</v>
       </c>
       <c r="C142" s="3">
-        <v>17.5</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D142" s="6">
-        <v>22.23</v>
+        <v>40.880000000000003</v>
       </c>
       <c r="E142">
         <v>2026</v>
@@ -3959,10 +3955,10 @@
         <v>147</v>
       </c>
       <c r="C143" s="3">
-        <v>17.670000000000002</v>
+        <v>28.24</v>
       </c>
       <c r="D143" s="6">
-        <v>21.71</v>
+        <v>34.65</v>
       </c>
       <c r="E143">
         <v>2026</v>
@@ -3979,10 +3975,10 @@
         <v>148</v>
       </c>
       <c r="C144" s="3">
-        <v>17.53</v>
+        <v>21.1</v>
       </c>
       <c r="D144" s="6">
-        <v>20.84</v>
+        <v>24.99</v>
       </c>
       <c r="E144">
         <v>2026</v>
@@ -3999,10 +3995,10 @@
         <v>149</v>
       </c>
       <c r="C145" s="3">
-        <v>28.49</v>
+        <v>36.49</v>
       </c>
       <c r="D145" s="6">
-        <v>33.97</v>
+        <v>43.1</v>
       </c>
       <c r="E145">
         <v>2026</v>
@@ -4019,10 +4015,10 @@
         <v>150</v>
       </c>
       <c r="C146" s="3">
-        <v>22.15</v>
+        <v>25.06</v>
       </c>
       <c r="D146" s="6">
-        <v>26.72</v>
+        <v>30.17</v>
       </c>
       <c r="E146">
         <v>2026</v>
@@ -4039,10 +4035,10 @@
         <v>151</v>
       </c>
       <c r="C147" s="3">
-        <v>21.48</v>
+        <v>24.55</v>
       </c>
       <c r="D147" s="6">
-        <v>24.61</v>
+        <v>27.87</v>
       </c>
       <c r="E147">
         <v>2026</v>
@@ -4059,10 +4055,10 @@
         <v>152</v>
       </c>
       <c r="C148" s="3">
-        <v>24.12</v>
+        <v>29.5</v>
       </c>
       <c r="D148" s="6">
-        <v>29.42</v>
+        <v>35.9</v>
       </c>
       <c r="E148">
         <v>2026</v>
@@ -4079,10 +4075,10 @@
         <v>153</v>
       </c>
       <c r="C149" s="3">
-        <v>19.16</v>
+        <v>27.86</v>
       </c>
       <c r="D149" s="6">
-        <v>24.04</v>
+        <v>34.909999999999997</v>
       </c>
       <c r="E149">
         <v>2026</v>
@@ -4099,10 +4095,10 @@
         <v>154</v>
       </c>
       <c r="C150" s="3">
-        <v>11.11</v>
+        <v>14.4</v>
       </c>
       <c r="D150" s="6">
-        <v>14.08</v>
+        <v>18.239999999999998</v>
       </c>
       <c r="E150">
         <v>2026</v>
@@ -4119,10 +4115,10 @@
         <v>155</v>
       </c>
       <c r="C151" s="3">
-        <v>12.35</v>
+        <v>12.06</v>
       </c>
       <c r="D151" s="6">
-        <v>14.83</v>
+        <v>14.51</v>
       </c>
       <c r="E151">
         <v>2026</v>
@@ -4139,10 +4135,10 @@
         <v>156</v>
       </c>
       <c r="C152" s="3">
-        <v>21.04</v>
+        <v>20.65</v>
       </c>
       <c r="D152" s="6">
-        <v>25.54</v>
+        <v>25.05</v>
       </c>
       <c r="E152">
         <v>2026</v>
@@ -4159,10 +4155,10 @@
         <v>157</v>
       </c>
       <c r="C153" s="3">
-        <v>21.5</v>
+        <v>21.39</v>
       </c>
       <c r="D153" s="6">
-        <v>26.88</v>
+        <v>26.7</v>
       </c>
       <c r="E153">
         <v>2026</v>
@@ -4179,10 +4175,10 @@
         <v>158</v>
       </c>
       <c r="C154" s="3">
-        <v>11.73</v>
+        <v>11.66</v>
       </c>
       <c r="D154" s="6">
-        <v>14.94</v>
+        <v>14.84</v>
       </c>
       <c r="E154">
         <v>2026</v>
@@ -4199,10 +4195,10 @@
         <v>159</v>
       </c>
       <c r="C155" s="3">
-        <v>14.34</v>
+        <v>15.11</v>
       </c>
       <c r="D155" s="6">
-        <v>17.38</v>
+        <v>18.28</v>
       </c>
       <c r="E155">
         <v>2026</v>
@@ -4219,10 +4215,10 @@
         <v>160</v>
       </c>
       <c r="C156" s="3">
-        <v>22.24</v>
+        <v>28.92</v>
       </c>
       <c r="D156" s="6">
-        <v>27.41</v>
+        <v>35.53</v>
       </c>
       <c r="E156">
         <v>2026</v>
@@ -4239,10 +4235,10 @@
         <v>161</v>
       </c>
       <c r="C157" s="3">
-        <v>14.91</v>
+        <v>19.04</v>
       </c>
       <c r="D157" s="6">
-        <v>18.899999999999999</v>
+        <v>24.12</v>
       </c>
       <c r="E157">
         <v>2026</v>
@@ -4259,10 +4255,10 @@
         <v>162</v>
       </c>
       <c r="C158" s="3">
-        <v>31.16</v>
+        <v>28.33</v>
       </c>
       <c r="D158" s="6">
-        <v>34.94</v>
+        <v>32.18</v>
       </c>
       <c r="E158">
         <v>2026</v>
@@ -4279,10 +4275,10 @@
         <v>163</v>
       </c>
       <c r="C159" s="3">
-        <v>28.83</v>
+        <v>43.77</v>
       </c>
       <c r="D159" s="6">
-        <v>36.479999999999997</v>
+        <v>55.27</v>
       </c>
       <c r="E159">
         <v>2026</v>
@@ -4299,10 +4295,10 @@
         <v>164</v>
       </c>
       <c r="C160" s="3">
-        <v>28.01</v>
+        <v>42.96</v>
       </c>
       <c r="D160" s="6">
-        <v>35.17</v>
+        <v>53.91</v>
       </c>
       <c r="E160">
         <v>2026</v>
@@ -4319,10 +4315,10 @@
         <v>165</v>
       </c>
       <c r="C161" s="3">
-        <v>23.18</v>
+        <v>30.26</v>
       </c>
       <c r="D161" s="6">
-        <v>28.26</v>
+        <v>36.42</v>
       </c>
       <c r="E161">
         <v>2026</v>
@@ -4339,10 +4335,10 @@
         <v>166</v>
       </c>
       <c r="C162" s="3">
-        <v>30</v>
+        <v>34.380000000000003</v>
       </c>
       <c r="D162" s="6">
-        <v>36.950000000000003</v>
+        <v>42.25</v>
       </c>
       <c r="E162">
         <v>2026</v>
@@ -4359,10 +4355,10 @@
         <v>167</v>
       </c>
       <c r="C163" s="3">
-        <v>20.3</v>
+        <v>24.35</v>
       </c>
       <c r="D163" s="6">
-        <v>24.52</v>
+        <v>29.33</v>
       </c>
       <c r="E163">
         <v>2026</v>
@@ -4379,10 +4375,10 @@
         <v>168</v>
       </c>
       <c r="C164" s="3">
-        <v>23.69</v>
+        <v>26.38</v>
       </c>
       <c r="D164" s="6">
-        <v>29.38</v>
+        <v>32.72</v>
       </c>
       <c r="E164">
         <v>2026</v>
@@ -4399,10 +4395,10 @@
         <v>169</v>
       </c>
       <c r="C165" s="3">
-        <v>27.5</v>
+        <v>44.84</v>
       </c>
       <c r="D165" s="6">
-        <v>33.369999999999997</v>
+        <v>53.87</v>
       </c>
       <c r="E165">
         <v>2026</v>
@@ -4419,10 +4415,10 @@
         <v>170</v>
       </c>
       <c r="C166" s="3">
-        <v>31.15</v>
+        <v>34.99</v>
       </c>
       <c r="D166" s="6">
-        <v>39.68</v>
+        <v>44.34</v>
       </c>
       <c r="E166">
         <v>2026</v>
@@ -4439,10 +4435,10 @@
         <v>171</v>
       </c>
       <c r="C167" s="3">
-        <v>12.61</v>
+        <v>21.2</v>
       </c>
       <c r="D167" s="6">
-        <v>15.82</v>
+        <v>26.56</v>
       </c>
       <c r="E167">
         <v>2026</v>
@@ -4459,10 +4455,10 @@
         <v>172</v>
       </c>
       <c r="C168" s="3">
-        <v>13.98</v>
+        <v>20.2</v>
       </c>
       <c r="D168" s="6">
-        <v>17.22</v>
+        <v>24.84</v>
       </c>
       <c r="E168">
         <v>2026</v>
@@ -4479,10 +4475,10 @@
         <v>173</v>
       </c>
       <c r="C169" s="3">
-        <v>15.18</v>
+        <v>21.87</v>
       </c>
       <c r="D169" s="6">
-        <v>18.82</v>
+        <v>27.03</v>
       </c>
       <c r="E169">
         <v>2026</v>
@@ -4499,10 +4495,10 @@
         <v>174</v>
       </c>
       <c r="C170" s="3">
-        <v>13.46</v>
+        <v>18.21</v>
       </c>
       <c r="D170" s="6">
-        <v>16.98</v>
+        <v>22.92</v>
       </c>
       <c r="E170">
         <v>2026</v>
@@ -4519,10 +4515,10 @@
         <v>175</v>
       </c>
       <c r="C171" s="3">
-        <v>11.55</v>
+        <v>21.3</v>
       </c>
       <c r="D171" s="6">
-        <v>14.6</v>
+        <v>26.87</v>
       </c>
       <c r="E171">
         <v>2026</v>
@@ -4539,10 +4535,10 @@
         <v>176</v>
       </c>
       <c r="C172" s="3">
-        <v>12.98</v>
+        <v>16.3</v>
       </c>
       <c r="D172" s="6">
-        <v>16.38</v>
+        <v>20.53</v>
       </c>
       <c r="E172">
         <v>2026</v>
@@ -4559,10 +4555,10 @@
         <v>177</v>
       </c>
       <c r="C173" s="3">
-        <v>26.37</v>
+        <v>29.38</v>
       </c>
       <c r="D173" s="6">
-        <v>32.86</v>
+        <v>36.54</v>
       </c>
       <c r="E173">
         <v>2026</v>
@@ -4579,10 +4575,10 @@
         <v>178</v>
       </c>
       <c r="C174" s="3">
-        <v>26.26</v>
+        <v>36.83</v>
       </c>
       <c r="D174" s="6">
-        <v>32.479999999999997</v>
+        <v>45.4</v>
       </c>
       <c r="E174">
         <v>2026</v>
@@ -4599,10 +4595,10 @@
         <v>179</v>
       </c>
       <c r="C175" s="3">
-        <v>30.06</v>
+        <v>39.67</v>
       </c>
       <c r="D175" s="6">
-        <v>35.53</v>
+        <v>46.73</v>
       </c>
       <c r="E175">
         <v>2026</v>
@@ -4619,10 +4615,10 @@
         <v>180</v>
       </c>
       <c r="C176" s="3">
-        <v>17.940000000000001</v>
+        <v>43.78</v>
       </c>
       <c r="D176" s="6">
-        <v>22.91</v>
+        <v>55.91</v>
       </c>
       <c r="E176">
         <v>2026</v>
@@ -4639,10 +4635,10 @@
         <v>181</v>
       </c>
       <c r="C177" s="3">
-        <v>25.66</v>
+        <v>41.59</v>
       </c>
       <c r="D177" s="6">
-        <v>32.770000000000003</v>
+        <v>53.33</v>
       </c>
       <c r="E177">
         <v>2026</v>
@@ -4659,10 +4655,10 @@
         <v>182</v>
       </c>
       <c r="C178" s="3">
-        <v>41.9</v>
+        <v>43.14</v>
       </c>
       <c r="D178" s="6">
-        <v>47.8</v>
+        <v>49.62</v>
       </c>
       <c r="E178">
         <v>2026</v>
@@ -4679,10 +4675,10 @@
         <v>183</v>
       </c>
       <c r="C179" s="3">
-        <v>26.12</v>
+        <v>37.4</v>
       </c>
       <c r="D179" s="6">
-        <v>32.51</v>
+        <v>47.53</v>
       </c>
       <c r="E179">
         <v>2026</v>
@@ -4699,10 +4695,10 @@
         <v>184</v>
       </c>
       <c r="C180" s="3">
-        <v>27.68</v>
+        <v>41.65</v>
       </c>
       <c r="D180" s="6">
-        <v>34.83</v>
+        <v>53.18</v>
       </c>
       <c r="E180">
         <v>2026</v>
@@ -4719,10 +4715,10 @@
         <v>185</v>
       </c>
       <c r="C181" s="3">
-        <v>32.17</v>
+        <v>37.04</v>
       </c>
       <c r="D181" s="6">
-        <v>37.64</v>
+        <v>42.99</v>
       </c>
       <c r="E181">
         <v>2026</v>
@@ -4739,10 +4735,10 @@
         <v>186</v>
       </c>
       <c r="C182" s="3">
-        <v>64.650000000000006</v>
+        <v>71.650000000000006</v>
       </c>
       <c r="D182" s="6">
-        <v>72.75</v>
+        <v>81.05</v>
       </c>
       <c r="E182">
         <v>2026</v>
@@ -4759,10 +4755,10 @@
         <v>187</v>
       </c>
       <c r="C183" s="3">
-        <v>49.41</v>
+        <v>57.34</v>
       </c>
       <c r="D183" s="6">
-        <v>55.19</v>
+        <v>64.17</v>
       </c>
       <c r="E183">
         <v>2026</v>
@@ -4779,10 +4775,10 @@
         <v>188</v>
       </c>
       <c r="C184" s="3">
-        <v>34.299999999999997</v>
+        <v>42.35</v>
       </c>
       <c r="D184" s="6">
-        <v>42.1</v>
+        <v>51.78</v>
       </c>
       <c r="E184">
         <v>2026</v>
@@ -4799,10 +4795,10 @@
         <v>189</v>
       </c>
       <c r="C185" s="3">
-        <v>128.19</v>
+        <v>128.41</v>
       </c>
       <c r="D185" s="6">
-        <v>165.79</v>
+        <v>166.01</v>
       </c>
       <c r="E185">
         <v>2026</v>
@@ -4819,10 +4815,10 @@
         <v>190</v>
       </c>
       <c r="C186" s="3">
-        <v>19.53</v>
+        <v>34.5</v>
       </c>
       <c r="D186" s="6">
-        <v>23.91</v>
+        <v>42.08</v>
       </c>
       <c r="E186">
         <v>2026</v>
@@ -4839,10 +4835,10 @@
         <v>191</v>
       </c>
       <c r="C187" s="3">
-        <v>20.14</v>
+        <v>24.19</v>
       </c>
       <c r="D187" s="6">
-        <v>24.99</v>
+        <v>29.96</v>
       </c>
       <c r="E187">
         <v>2026</v>
@@ -4859,10 +4855,10 @@
         <v>192</v>
       </c>
       <c r="C188" s="3">
-        <v>17.87</v>
+        <v>21.48</v>
       </c>
       <c r="D188" s="6">
-        <v>22.64</v>
+        <v>27.19</v>
       </c>
       <c r="E188">
         <v>2026</v>
@@ -4879,10 +4875,10 @@
         <v>193</v>
       </c>
       <c r="C189" s="3">
-        <v>25.04</v>
+        <v>32.44</v>
       </c>
       <c r="D189" s="6">
-        <v>29.56</v>
+        <v>38.28</v>
       </c>
       <c r="E189">
         <v>2026</v>
@@ -4899,10 +4895,10 @@
         <v>194</v>
       </c>
       <c r="C190" s="3">
-        <v>34.06</v>
+        <v>39.229999999999997</v>
       </c>
       <c r="D190" s="6">
-        <v>37.42</v>
+        <v>42.6</v>
       </c>
       <c r="E190">
         <v>2026</v>
@@ -4919,10 +4915,10 @@
         <v>195</v>
       </c>
       <c r="C191" s="3">
-        <v>15.23</v>
+        <v>29.77</v>
       </c>
       <c r="D191" s="6">
-        <v>19.14</v>
+        <v>37.33</v>
       </c>
       <c r="E191">
         <v>2026</v>
@@ -4939,10 +4935,10 @@
         <v>196</v>
       </c>
       <c r="C192" s="3">
-        <v>15.88</v>
+        <v>35.229999999999997</v>
       </c>
       <c r="D192" s="6">
-        <v>19.98</v>
+        <v>44.29</v>
       </c>
       <c r="E192">
         <v>2026</v>
@@ -4959,10 +4955,10 @@
         <v>197</v>
       </c>
       <c r="C193" s="3">
-        <v>39.89</v>
+        <v>40.18</v>
       </c>
       <c r="D193" s="6">
-        <v>44.65</v>
+        <v>45.12</v>
       </c>
       <c r="E193">
         <v>2026</v>
@@ -4979,10 +4975,10 @@
         <v>198</v>
       </c>
       <c r="C194" s="3">
-        <v>23.05</v>
+        <v>23.28</v>
       </c>
       <c r="D194" s="6">
-        <v>26.89</v>
+        <v>27.27</v>
       </c>
       <c r="E194">
         <v>2026</v>
@@ -4999,10 +4995,10 @@
         <v>199</v>
       </c>
       <c r="C195" s="3">
-        <v>13.72</v>
+        <v>17.760000000000002</v>
       </c>
       <c r="D195" s="6">
-        <v>17.2</v>
+        <v>22.24</v>
       </c>
       <c r="E195">
         <v>2026</v>
@@ -5019,10 +5015,10 @@
         <v>200</v>
       </c>
       <c r="C196" s="3">
-        <v>39.32</v>
+        <v>40.06</v>
       </c>
       <c r="D196" s="6">
-        <v>44.11</v>
+        <v>45.35</v>
       </c>
       <c r="E196">
         <v>2026</v>
@@ -5039,10 +5035,10 @@
         <v>201</v>
       </c>
       <c r="C197" s="3">
-        <v>15.84</v>
+        <v>22.91</v>
       </c>
       <c r="D197" s="6">
-        <v>19.64</v>
+        <v>28.39</v>
       </c>
       <c r="E197">
         <v>2026</v>
@@ -5059,10 +5055,10 @@
         <v>202</v>
       </c>
       <c r="C198" s="3">
-        <v>20.81</v>
+        <v>32.380000000000003</v>
       </c>
       <c r="D198" s="6">
-        <v>25.09</v>
+        <v>38.880000000000003</v>
       </c>
       <c r="E198">
         <v>2026</v>
@@ -5079,10 +5075,10 @@
         <v>203</v>
       </c>
       <c r="C199" s="3">
-        <v>32</v>
+        <v>35.71</v>
       </c>
       <c r="D199" s="6">
-        <v>35.61</v>
+        <v>39.5</v>
       </c>
       <c r="E199">
         <v>2026</v>
@@ -5099,10 +5095,10 @@
         <v>204</v>
       </c>
       <c r="C200" s="3">
-        <v>22.13</v>
+        <v>22.09</v>
       </c>
       <c r="D200" s="6">
-        <v>25.69</v>
+        <v>25.67</v>
       </c>
       <c r="E200">
         <v>2026</v>
@@ -5119,10 +5115,10 @@
         <v>202</v>
       </c>
       <c r="C201" s="3">
-        <v>20.81</v>
+        <v>32.380000000000003</v>
       </c>
       <c r="D201" s="6">
-        <v>25.09</v>
+        <v>38.880000000000003</v>
       </c>
       <c r="E201">
         <v>2026</v>
@@ -5139,10 +5135,10 @@
         <v>6</v>
       </c>
       <c r="C202" s="3">
-        <v>23.76</v>
+        <v>33.99</v>
       </c>
       <c r="D202" s="6">
-        <v>28.85</v>
+        <v>41.26</v>
       </c>
       <c r="E202">
         <v>2026</v>
@@ -5159,10 +5155,10 @@
         <v>7</v>
       </c>
       <c r="C203" s="3">
-        <v>26.39</v>
+        <v>41.51</v>
       </c>
       <c r="D203" s="6">
-        <v>32.44</v>
+        <v>50.98</v>
       </c>
       <c r="E203">
         <v>2026</v>
@@ -5179,10 +5175,10 @@
         <v>8</v>
       </c>
       <c r="C204" s="3">
-        <v>23.31</v>
+        <v>28.27</v>
       </c>
       <c r="D204" s="6">
-        <v>28.08</v>
+        <v>34.04</v>
       </c>
       <c r="E204">
         <v>2026</v>
@@ -5199,10 +5195,10 @@
         <v>9</v>
       </c>
       <c r="C205" s="3">
-        <v>14.63</v>
+        <v>14.69</v>
       </c>
       <c r="D205" s="6">
-        <v>18.2</v>
+        <v>18.25</v>
       </c>
       <c r="E205">
         <v>2026</v>
@@ -5219,10 +5215,10 @@
         <v>10</v>
       </c>
       <c r="C206" s="3">
-        <v>37.340000000000003</v>
+        <v>36.4</v>
       </c>
       <c r="D206" s="6">
-        <v>41.9</v>
+        <v>41.41</v>
       </c>
       <c r="E206">
         <v>2026</v>
@@ -5239,10 +5235,10 @@
         <v>11</v>
       </c>
       <c r="C207" s="3">
-        <v>36.1</v>
+        <v>34.619999999999997</v>
       </c>
       <c r="D207" s="6">
-        <v>40.03</v>
+        <v>38.82</v>
       </c>
       <c r="E207">
         <v>2026</v>
@@ -5259,10 +5255,10 @@
         <v>12</v>
       </c>
       <c r="C208" s="3">
-        <v>0</v>
+        <v>928.24</v>
       </c>
       <c r="D208" s="6">
-        <v>0</v>
+        <v>1183.05</v>
       </c>
       <c r="E208">
         <v>2026</v>
@@ -5279,10 +5275,10 @@
         <v>13</v>
       </c>
       <c r="C209" s="3">
-        <v>0</v>
+        <v>27.45</v>
       </c>
       <c r="D209" s="6">
-        <v>0</v>
+        <v>33.409999999999997</v>
       </c>
       <c r="E209">
         <v>2026</v>
@@ -5299,10 +5295,10 @@
         <v>14</v>
       </c>
       <c r="C210" s="3">
-        <v>19.850000000000001</v>
+        <v>23.11</v>
       </c>
       <c r="D210" s="6">
-        <v>24.31</v>
+        <v>28.36</v>
       </c>
       <c r="E210">
         <v>2026</v>
@@ -5319,10 +5315,10 @@
         <v>15</v>
       </c>
       <c r="C211" s="3">
-        <v>24.82</v>
+        <v>30.2</v>
       </c>
       <c r="D211" s="6">
-        <v>29.72</v>
+        <v>36.299999999999997</v>
       </c>
       <c r="E211">
         <v>2026</v>
@@ -5339,10 +5335,10 @@
         <v>16</v>
       </c>
       <c r="C212" s="3">
-        <v>35.200000000000003</v>
+        <v>60.09</v>
       </c>
       <c r="D212" s="6">
-        <v>43.63</v>
+        <v>74.97</v>
       </c>
       <c r="E212">
         <v>2026</v>
@@ -5359,10 +5355,10 @@
         <v>17</v>
       </c>
       <c r="C213" s="3">
-        <v>26.64</v>
+        <v>27.99</v>
       </c>
       <c r="D213" s="6">
-        <v>29.91</v>
+        <v>31.9</v>
       </c>
       <c r="E213">
         <v>2026</v>
@@ -5379,10 +5375,10 @@
         <v>18</v>
       </c>
       <c r="C214" s="3">
-        <v>22.84</v>
+        <v>21.18</v>
       </c>
       <c r="D214" s="6">
-        <v>25.75</v>
+        <v>24.13</v>
       </c>
       <c r="E214">
         <v>2026</v>
@@ -5399,10 +5395,10 @@
         <v>19</v>
       </c>
       <c r="C215" s="3">
-        <v>17.66</v>
+        <v>17.93</v>
       </c>
       <c r="D215" s="6">
-        <v>21.61</v>
+        <v>21.99</v>
       </c>
       <c r="E215">
         <v>2026</v>
@@ -5419,10 +5415,10 @@
         <v>20</v>
       </c>
       <c r="C216" s="3">
-        <v>17.920000000000002</v>
+        <v>18.25</v>
       </c>
       <c r="D216" s="6">
-        <v>22.43</v>
+        <v>22.85</v>
       </c>
       <c r="E216">
         <v>2026</v>
@@ -5439,10 +5435,10 @@
         <v>21</v>
       </c>
       <c r="C217" s="3">
-        <v>12.42</v>
+        <v>12.61</v>
       </c>
       <c r="D217" s="6">
-        <v>15.08</v>
+        <v>15.31</v>
       </c>
       <c r="E217">
         <v>2026</v>
@@ -5459,10 +5455,10 @@
         <v>22</v>
       </c>
       <c r="C218" s="3">
-        <v>33.47</v>
+        <v>30.28</v>
       </c>
       <c r="D218" s="6">
-        <v>36.25</v>
+        <v>33.090000000000003</v>
       </c>
       <c r="E218">
         <v>2026</v>
@@ -5479,10 +5475,10 @@
         <v>23</v>
       </c>
       <c r="C219" s="3">
-        <v>36.659999999999997</v>
+        <v>33.71</v>
       </c>
       <c r="D219" s="6">
-        <v>39.96</v>
+        <v>37.049999999999997</v>
       </c>
       <c r="E219">
         <v>2026</v>
@@ -5499,10 +5495,10 @@
         <v>24</v>
       </c>
       <c r="C220" s="3">
-        <v>38.65</v>
+        <v>35.869999999999997</v>
       </c>
       <c r="D220" s="6">
-        <v>43.34</v>
+        <v>40.78</v>
       </c>
       <c r="E220">
         <v>2026</v>
@@ -5519,10 +5515,10 @@
         <v>25</v>
       </c>
       <c r="C221" s="3">
-        <v>46.82</v>
+        <v>42.82</v>
       </c>
       <c r="D221" s="6">
-        <v>51.14</v>
+        <v>47.15</v>
       </c>
       <c r="E221">
         <v>2026</v>
@@ -5539,10 +5535,10 @@
         <v>26</v>
       </c>
       <c r="C222" s="3">
-        <v>36.28</v>
+        <v>46.68</v>
       </c>
       <c r="D222" s="6">
-        <v>42.69</v>
+        <v>55.09</v>
       </c>
       <c r="E222">
         <v>2026</v>
@@ -5559,10 +5555,10 @@
         <v>27</v>
       </c>
       <c r="C223" s="3">
-        <v>23.25</v>
+        <v>57.66</v>
       </c>
       <c r="D223" s="6">
-        <v>28.33</v>
+        <v>65.61</v>
       </c>
       <c r="E223">
         <v>2026</v>
@@ -5579,10 +5575,10 @@
         <v>28</v>
       </c>
       <c r="C224" s="3">
-        <v>45.6</v>
+        <v>53.68</v>
       </c>
       <c r="D224" s="6">
-        <v>51.77</v>
+        <v>61.9</v>
       </c>
       <c r="E224">
         <v>2026</v>
@@ -5599,10 +5595,10 @@
         <v>29</v>
       </c>
       <c r="C225" s="3">
-        <v>37.18</v>
+        <v>47.85</v>
       </c>
       <c r="D225" s="6">
-        <v>43.41</v>
+        <v>57.15</v>
       </c>
       <c r="E225">
         <v>2026</v>
@@ -5619,10 +5615,10 @@
         <v>30</v>
       </c>
       <c r="C226" s="3">
-        <v>147.77000000000001</v>
+        <v>143.57</v>
       </c>
       <c r="D226" s="6">
-        <v>165</v>
+        <v>163.69</v>
       </c>
       <c r="E226">
         <v>2026</v>
@@ -5639,10 +5635,10 @@
         <v>31</v>
       </c>
       <c r="C227" s="3">
-        <v>24.61</v>
+        <v>29.99</v>
       </c>
       <c r="D227" s="6">
-        <v>29.93</v>
+        <v>36.33</v>
       </c>
       <c r="E227">
         <v>2026</v>
@@ -5659,10 +5655,10 @@
         <v>32</v>
       </c>
       <c r="C228" s="3">
-        <v>26.86</v>
+        <v>30.27</v>
       </c>
       <c r="D228" s="6">
-        <v>33.64</v>
+        <v>37.909999999999997</v>
       </c>
       <c r="E228">
         <v>2026</v>
@@ -5679,10 +5675,10 @@
         <v>33</v>
       </c>
       <c r="C229" s="3">
-        <v>40.31</v>
+        <v>41.27</v>
       </c>
       <c r="D229" s="6">
-        <v>47.49</v>
+        <v>49.19</v>
       </c>
       <c r="E229">
         <v>2026</v>
@@ -5699,10 +5695,10 @@
         <v>34</v>
       </c>
       <c r="C230" s="3">
-        <v>59.06</v>
+        <v>64.13</v>
       </c>
       <c r="D230" s="6">
-        <v>67.319999999999993</v>
+        <v>73.47</v>
       </c>
       <c r="E230">
         <v>2026</v>
@@ -5719,10 +5715,10 @@
         <v>35</v>
       </c>
       <c r="C231" s="3">
-        <v>42.37</v>
+        <v>40.06</v>
       </c>
       <c r="D231" s="6">
-        <v>48.55</v>
+        <v>46.34</v>
       </c>
       <c r="E231">
         <v>2026</v>
@@ -5739,10 +5735,10 @@
         <v>36</v>
       </c>
       <c r="C232" s="3">
-        <v>39.06</v>
+        <v>37.25</v>
       </c>
       <c r="D232" s="6">
-        <v>43.83</v>
+        <v>42.32</v>
       </c>
       <c r="E232">
         <v>2026</v>
@@ -5759,10 +5755,10 @@
         <v>37</v>
       </c>
       <c r="C233" s="3">
-        <v>38.049999999999997</v>
+        <v>36.28</v>
       </c>
       <c r="D233" s="6">
-        <v>42.34</v>
+        <v>40.81</v>
       </c>
       <c r="E233">
         <v>2026</v>
@@ -5779,10 +5775,10 @@
         <v>38</v>
       </c>
       <c r="C234" s="3">
-        <v>44.44</v>
+        <v>40.67</v>
       </c>
       <c r="D234" s="6">
-        <v>49.19</v>
+        <v>45.52</v>
       </c>
       <c r="E234">
         <v>2026</v>
@@ -5799,10 +5795,10 @@
         <v>39</v>
       </c>
       <c r="C235" s="3">
-        <v>20.64</v>
+        <v>29.32</v>
       </c>
       <c r="D235" s="6">
-        <v>25.02</v>
+        <v>35.57</v>
       </c>
       <c r="E235">
         <v>2026</v>
@@ -5819,10 +5815,10 @@
         <v>40</v>
       </c>
       <c r="C236" s="3">
-        <v>30.74</v>
+        <v>44.55</v>
       </c>
       <c r="D236" s="6">
-        <v>35.44</v>
+        <v>51.36</v>
       </c>
       <c r="E236">
         <v>2026</v>
@@ -5839,10 +5835,10 @@
         <v>41</v>
       </c>
       <c r="C237" s="3">
-        <v>27.83</v>
+        <v>24.3</v>
       </c>
       <c r="D237" s="6">
-        <v>31.96</v>
+        <v>28.22</v>
       </c>
       <c r="E237">
         <v>2026</v>
@@ -5859,10 +5855,10 @@
         <v>42</v>
       </c>
       <c r="C238" s="3">
-        <v>14.16</v>
+        <v>19.34</v>
       </c>
       <c r="D238" s="6">
-        <v>17.829999999999998</v>
+        <v>24.36</v>
       </c>
       <c r="E238">
         <v>2026</v>
@@ -5879,10 +5875,10 @@
         <v>43</v>
       </c>
       <c r="C239" s="3">
-        <v>18.53</v>
+        <v>20.58</v>
       </c>
       <c r="D239" s="6">
-        <v>23.63</v>
+        <v>26.25</v>
       </c>
       <c r="E239">
         <v>2026</v>
@@ -5899,10 +5895,10 @@
         <v>44</v>
       </c>
       <c r="C240" s="3">
-        <v>24.53</v>
+        <v>37.15</v>
       </c>
       <c r="D240" s="6">
-        <v>30.56</v>
+        <v>46.36</v>
       </c>
       <c r="E240">
         <v>2026</v>
@@ -5919,10 +5915,10 @@
         <v>45</v>
       </c>
       <c r="C241" s="3">
-        <v>71.930000000000007</v>
+        <v>61.96</v>
       </c>
       <c r="D241" s="6">
-        <v>75.680000000000007</v>
+        <v>66.5</v>
       </c>
       <c r="E241">
         <v>2026</v>
@@ -5939,10 +5935,10 @@
         <v>46</v>
       </c>
       <c r="C242" s="3">
-        <v>19.809999999999999</v>
+        <v>35.659999999999997</v>
       </c>
       <c r="D242" s="6">
-        <v>24.53</v>
+        <v>44.16</v>
       </c>
       <c r="E242">
         <v>2026</v>
@@ -5959,10 +5955,10 @@
         <v>47</v>
       </c>
       <c r="C243" s="3">
-        <v>22.42</v>
+        <v>20.76</v>
       </c>
       <c r="D243" s="6">
-        <v>25.79</v>
+        <v>24.08</v>
       </c>
       <c r="E243">
         <v>2026</v>
@@ -5979,10 +5975,10 @@
         <v>48</v>
       </c>
       <c r="C244" s="3">
-        <v>31.74</v>
+        <v>39.54</v>
       </c>
       <c r="D244" s="6">
-        <v>38.96</v>
+        <v>48.72</v>
       </c>
       <c r="E244">
         <v>2026</v>
@@ -5999,10 +5995,10 @@
         <v>49</v>
       </c>
       <c r="C245" s="3">
-        <v>25.59</v>
+        <v>28.47</v>
       </c>
       <c r="D245" s="6">
-        <v>32.47</v>
+        <v>36.15</v>
       </c>
       <c r="E245">
         <v>2026</v>
@@ -6019,7 +6015,7 @@
         <v>50</v>
       </c>
       <c r="C246" s="3">
-        <v>26.08</v>
+        <v>26.09</v>
       </c>
       <c r="D246" s="6">
         <v>33.15</v>
@@ -6039,10 +6035,10 @@
         <v>51</v>
       </c>
       <c r="C247" s="3">
-        <v>15.12</v>
+        <v>15.37</v>
       </c>
       <c r="D247" s="6">
-        <v>19.12</v>
+        <v>19.43</v>
       </c>
       <c r="E247">
         <v>2026</v>
@@ -6059,10 +6055,10 @@
         <v>52</v>
       </c>
       <c r="C248" s="3">
-        <v>25.81</v>
+        <v>33.79</v>
       </c>
       <c r="D248" s="6">
-        <v>31.01</v>
+        <v>40.590000000000003</v>
       </c>
       <c r="E248">
         <v>2026</v>
@@ -6079,10 +6075,10 @@
         <v>53</v>
       </c>
       <c r="C249" s="3">
-        <v>17.98</v>
+        <v>29.25</v>
       </c>
       <c r="D249" s="6">
-        <v>22.58</v>
+        <v>36.74</v>
       </c>
       <c r="E249">
         <v>2026</v>
@@ -6099,10 +6095,10 @@
         <v>54</v>
       </c>
       <c r="C250" s="3">
-        <v>39.049999999999997</v>
+        <v>34.86</v>
       </c>
       <c r="D250" s="6">
-        <v>43.48</v>
+        <v>39.33</v>
       </c>
       <c r="E250">
         <v>2026</v>
@@ -6119,10 +6115,10 @@
         <v>55</v>
       </c>
       <c r="C251" s="3">
-        <v>46.75</v>
+        <v>32.130000000000003</v>
       </c>
       <c r="D251" s="6">
-        <v>52.98</v>
+        <v>36.96</v>
       </c>
       <c r="E251">
         <v>2026</v>
@@ -6139,10 +6135,10 @@
         <v>56</v>
       </c>
       <c r="C252" s="3">
-        <v>51.34</v>
+        <v>47.8</v>
       </c>
       <c r="D252" s="6">
-        <v>55.54</v>
+        <v>52.18</v>
       </c>
       <c r="E252">
         <v>2026</v>
@@ -6159,10 +6155,10 @@
         <v>57</v>
       </c>
       <c r="C253" s="3">
-        <v>40.29</v>
+        <v>54.66</v>
       </c>
       <c r="D253" s="6">
-        <v>47.18</v>
+        <v>65.89</v>
       </c>
       <c r="E253">
         <v>2026</v>
@@ -6179,10 +6175,10 @@
         <v>58</v>
       </c>
       <c r="C254" s="3">
-        <v>32.520000000000003</v>
+        <v>38.119999999999997</v>
       </c>
       <c r="D254" s="6">
-        <v>38.33</v>
+        <v>45.57</v>
       </c>
       <c r="E254">
         <v>2026</v>
@@ -6199,10 +6195,10 @@
         <v>59</v>
       </c>
       <c r="C255" s="3">
-        <v>38.979999999999997</v>
+        <v>39.96</v>
       </c>
       <c r="D255" s="6">
-        <v>43.45</v>
+        <v>45.41</v>
       </c>
       <c r="E255">
         <v>2026</v>
@@ -6219,10 +6215,10 @@
         <v>60</v>
       </c>
       <c r="C256" s="3">
-        <v>35.01</v>
+        <v>29.65</v>
       </c>
       <c r="D256" s="6">
-        <v>38.11</v>
+        <v>32.76</v>
       </c>
       <c r="E256">
         <v>2026</v>
@@ -6239,10 +6235,10 @@
         <v>61</v>
       </c>
       <c r="C257" s="3">
-        <v>14.22</v>
+        <v>32.97</v>
       </c>
       <c r="D257" s="6">
-        <v>17.91</v>
+        <v>41.53</v>
       </c>
       <c r="E257">
         <v>2026</v>
@@ -6259,10 +6255,10 @@
         <v>62</v>
       </c>
       <c r="C258" s="3">
-        <v>15.1</v>
+        <v>31.36</v>
       </c>
       <c r="D258" s="6">
-        <v>18.77</v>
+        <v>39</v>
       </c>
       <c r="E258">
         <v>2026</v>
@@ -6279,10 +6275,10 @@
         <v>63</v>
       </c>
       <c r="C259" s="3">
-        <v>14.37</v>
+        <v>25.74</v>
       </c>
       <c r="D259" s="6">
-        <v>18.14</v>
+        <v>32.49</v>
       </c>
       <c r="E259">
         <v>2026</v>
@@ -6299,10 +6295,10 @@
         <v>64</v>
       </c>
       <c r="C260" s="3">
-        <v>12.39</v>
+        <v>26.45</v>
       </c>
       <c r="D260" s="6">
-        <v>15.59</v>
+        <v>33.270000000000003</v>
       </c>
       <c r="E260">
         <v>2026</v>
@@ -6319,10 +6315,10 @@
         <v>65</v>
       </c>
       <c r="C261" s="3">
-        <v>20.81</v>
+        <v>33.32</v>
       </c>
       <c r="D261" s="6">
-        <v>25.55</v>
+        <v>40.909999999999997</v>
       </c>
       <c r="E261">
         <v>2026</v>
@@ -6339,10 +6335,10 @@
         <v>66</v>
       </c>
       <c r="C262" s="3">
-        <v>24.13</v>
+        <v>25.67</v>
       </c>
       <c r="D262" s="6">
-        <v>30.64</v>
+        <v>32.6</v>
       </c>
       <c r="E262">
         <v>2026</v>
@@ -6359,10 +6355,10 @@
         <v>67</v>
       </c>
       <c r="C263" s="3">
-        <v>16.059999999999999</v>
+        <v>24.27</v>
       </c>
       <c r="D263" s="6">
-        <v>20.09</v>
+        <v>30.36</v>
       </c>
       <c r="E263">
         <v>2026</v>
@@ -6379,10 +6375,10 @@
         <v>68</v>
       </c>
       <c r="C264" s="3">
-        <v>15.09</v>
+        <v>18.62</v>
       </c>
       <c r="D264" s="6">
-        <v>19.18</v>
+        <v>23.67</v>
       </c>
       <c r="E264">
         <v>2026</v>
@@ -6399,10 +6395,10 @@
         <v>69</v>
       </c>
       <c r="C265" s="3">
-        <v>18.62</v>
+        <v>24.88</v>
       </c>
       <c r="D265" s="6">
-        <v>22.93</v>
+        <v>30.56</v>
       </c>
       <c r="E265">
         <v>2026</v>
@@ -6419,10 +6415,10 @@
         <v>70</v>
       </c>
       <c r="C266" s="3">
-        <v>20.51</v>
+        <v>28.75</v>
       </c>
       <c r="D266" s="6">
-        <v>25.25</v>
+        <v>35.42</v>
       </c>
       <c r="E266">
         <v>2026</v>
@@ -6439,10 +6435,10 @@
         <v>71</v>
       </c>
       <c r="C267" s="3">
-        <v>17.489999999999998</v>
+        <v>22.14</v>
       </c>
       <c r="D267" s="6">
-        <v>21.63</v>
+        <v>27.37</v>
       </c>
       <c r="E267">
         <v>2026</v>
@@ -6459,10 +6455,10 @@
         <v>72</v>
       </c>
       <c r="C268" s="3">
-        <v>24.09</v>
+        <v>28.54</v>
       </c>
       <c r="D268" s="6">
-        <v>28.99</v>
+        <v>34.380000000000003</v>
       </c>
       <c r="E268">
         <v>2026</v>
@@ -6479,10 +6475,10 @@
         <v>73</v>
       </c>
       <c r="C269" s="3">
-        <v>27.77</v>
+        <v>38.619999999999997</v>
       </c>
       <c r="D269" s="6">
-        <v>32.69</v>
+        <v>45.49</v>
       </c>
       <c r="E269">
         <v>2026</v>
@@ -6499,10 +6495,10 @@
         <v>74</v>
       </c>
       <c r="C270" s="3">
-        <v>29.33</v>
+        <v>34.51</v>
       </c>
       <c r="D270" s="6">
-        <v>36.619999999999997</v>
+        <v>43.1</v>
       </c>
       <c r="E270">
         <v>2026</v>
@@ -6519,10 +6515,10 @@
         <v>75</v>
       </c>
       <c r="C271" s="3">
-        <v>25.97</v>
+        <v>29.05</v>
       </c>
       <c r="D271" s="6">
-        <v>31.15</v>
+        <v>34.83</v>
       </c>
       <c r="E271">
         <v>2026</v>
@@ -6539,10 +6535,10 @@
         <v>76</v>
       </c>
       <c r="C272" s="3">
-        <v>17.16</v>
+        <v>27.59</v>
       </c>
       <c r="D272" s="6">
-        <v>21.57</v>
+        <v>34.67</v>
       </c>
       <c r="E272">
         <v>2026</v>
@@ -6559,10 +6555,10 @@
         <v>77</v>
       </c>
       <c r="C273" s="3">
-        <v>26.61</v>
+        <v>38.979999999999997</v>
       </c>
       <c r="D273" s="6">
-        <v>33.32</v>
+        <v>48.84</v>
       </c>
       <c r="E273">
         <v>2026</v>
@@ -6579,10 +6575,10 @@
         <v>78</v>
       </c>
       <c r="C274" s="3">
-        <v>26.05</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="D274" s="6">
-        <v>32.22</v>
+        <v>39.75</v>
       </c>
       <c r="E274">
         <v>2026</v>
@@ -6599,10 +6595,10 @@
         <v>79</v>
       </c>
       <c r="C275" s="3">
-        <v>21.19</v>
+        <v>24.31</v>
       </c>
       <c r="D275" s="6">
-        <v>26.02</v>
+        <v>29.89</v>
       </c>
       <c r="E275">
         <v>2026</v>
@@ -6619,10 +6615,10 @@
         <v>80</v>
       </c>
       <c r="C276" s="3">
-        <v>28.22</v>
+        <v>37.21</v>
       </c>
       <c r="D276" s="6">
-        <v>35.04</v>
+        <v>46.2</v>
       </c>
       <c r="E276">
         <v>2026</v>
@@ -6639,10 +6635,10 @@
         <v>81</v>
       </c>
       <c r="C277" s="3">
-        <v>20.02</v>
+        <v>26.18</v>
       </c>
       <c r="D277" s="6">
-        <v>24.63</v>
+        <v>32.159999999999997</v>
       </c>
       <c r="E277">
         <v>2026</v>
@@ -6659,10 +6655,10 @@
         <v>82</v>
       </c>
       <c r="C278" s="3">
-        <v>28.07</v>
+        <v>29.45</v>
       </c>
       <c r="D278" s="6">
-        <v>34.99</v>
+        <v>36.71</v>
       </c>
       <c r="E278">
         <v>2026</v>
@@ -6679,10 +6675,10 @@
         <v>83</v>
       </c>
       <c r="C279" s="3">
-        <v>30.75</v>
+        <v>56.8</v>
       </c>
       <c r="D279" s="6">
-        <v>37.72</v>
+        <v>69.78</v>
       </c>
       <c r="E279">
         <v>2026</v>
@@ -6699,10 +6695,10 @@
         <v>84</v>
       </c>
       <c r="C280" s="3">
-        <v>16.32</v>
+        <v>23.6</v>
       </c>
       <c r="D280" s="6">
-        <v>20.03</v>
+        <v>28.95</v>
       </c>
       <c r="E280">
         <v>2026</v>
@@ -6719,10 +6715,10 @@
         <v>85</v>
       </c>
       <c r="C281" s="3">
-        <v>19.29</v>
+        <v>26.15</v>
       </c>
       <c r="D281" s="6">
-        <v>24.35</v>
+        <v>33.020000000000003</v>
       </c>
       <c r="E281">
         <v>2026</v>
@@ -6739,10 +6735,10 @@
         <v>86</v>
       </c>
       <c r="C282" s="3">
-        <v>18.14</v>
+        <v>29.04</v>
       </c>
       <c r="D282" s="6">
-        <v>22.37</v>
+        <v>35.79</v>
       </c>
       <c r="E282">
         <v>2026</v>
@@ -6759,10 +6755,10 @@
         <v>87</v>
       </c>
       <c r="C283" s="3">
-        <v>34.82</v>
+        <v>30.48</v>
       </c>
       <c r="D283" s="6">
-        <v>39.26</v>
+        <v>34.89</v>
       </c>
       <c r="E283">
         <v>2026</v>
@@ -6779,10 +6775,10 @@
         <v>88</v>
       </c>
       <c r="C284" s="3">
-        <v>46.6</v>
+        <v>42</v>
       </c>
       <c r="D284" s="6">
-        <v>50.61</v>
+        <v>46.01</v>
       </c>
       <c r="E284">
         <v>2026</v>
@@ -6799,10 +6795,10 @@
         <v>89</v>
       </c>
       <c r="C285" s="3">
-        <v>40.020000000000003</v>
+        <v>36.33</v>
       </c>
       <c r="D285" s="6">
-        <v>44.29</v>
+        <v>40.79</v>
       </c>
       <c r="E285">
         <v>2026</v>
@@ -6819,10 +6815,10 @@
         <v>90</v>
       </c>
       <c r="C286" s="3">
-        <v>26.99</v>
+        <v>24.91</v>
       </c>
       <c r="D286" s="6">
-        <v>31.75</v>
+        <v>29.62</v>
       </c>
       <c r="E286">
         <v>2026</v>
@@ -6839,10 +6835,10 @@
         <v>91</v>
       </c>
       <c r="C287" s="3">
-        <v>38.24</v>
+        <v>33.659999999999997</v>
       </c>
       <c r="D287" s="6">
-        <v>42.53</v>
+        <v>37.909999999999997</v>
       </c>
       <c r="E287">
         <v>2026</v>
@@ -6859,10 +6855,10 @@
         <v>92</v>
       </c>
       <c r="C288" s="3">
-        <v>36.29</v>
+        <v>32.869999999999997</v>
       </c>
       <c r="D288" s="6">
-        <v>41.77</v>
+        <v>38.25</v>
       </c>
       <c r="E288">
         <v>2026</v>
@@ -6879,10 +6875,10 @@
         <v>93</v>
       </c>
       <c r="C289" s="3">
-        <v>28.85</v>
+        <v>37.85</v>
       </c>
       <c r="D289" s="6">
-        <v>34.47</v>
+        <v>45.16</v>
       </c>
       <c r="E289">
         <v>2026</v>
@@ -6899,10 +6895,10 @@
         <v>94</v>
       </c>
       <c r="C290" s="3">
-        <v>28.36</v>
+        <v>35.450000000000003</v>
       </c>
       <c r="D290" s="6">
-        <v>35.67</v>
+        <v>44.61</v>
       </c>
       <c r="E290">
         <v>2026</v>
@@ -6919,10 +6915,10 @@
         <v>95</v>
       </c>
       <c r="C291" s="3">
-        <v>33.83</v>
+        <v>46.89</v>
       </c>
       <c r="D291" s="6">
-        <v>41.04</v>
+        <v>56.83</v>
       </c>
       <c r="E291">
         <v>2026</v>
@@ -6939,10 +6935,10 @@
         <v>96</v>
       </c>
       <c r="C292" s="3">
-        <v>31.63</v>
+        <v>43.74</v>
       </c>
       <c r="D292" s="6">
-        <v>38.46</v>
+        <v>53.21</v>
       </c>
       <c r="E292">
         <v>2026</v>
@@ -6959,10 +6955,10 @@
         <v>97</v>
       </c>
       <c r="C293" s="3">
-        <v>64.67</v>
+        <v>63.58</v>
       </c>
       <c r="D293" s="6">
-        <v>72.34</v>
+        <v>71.97</v>
       </c>
       <c r="E293">
         <v>2026</v>
@@ -6979,10 +6975,10 @@
         <v>98</v>
       </c>
       <c r="C294" s="3">
-        <v>32.97</v>
+        <v>43.18</v>
       </c>
       <c r="D294" s="6">
-        <v>38.93</v>
+        <v>51.01</v>
       </c>
       <c r="E294">
         <v>2026</v>
@@ -6999,10 +6995,10 @@
         <v>99</v>
       </c>
       <c r="C295" s="3">
-        <v>48.52</v>
+        <v>45.14</v>
       </c>
       <c r="D295" s="6">
-        <v>53.72</v>
+        <v>50.69</v>
       </c>
       <c r="E295">
         <v>2026</v>
@@ -7019,10 +7015,10 @@
         <v>100</v>
       </c>
       <c r="C296" s="3">
-        <v>64.67</v>
+        <v>61.46</v>
       </c>
       <c r="D296" s="6">
-        <v>71.53</v>
+        <v>68.760000000000005</v>
       </c>
       <c r="E296">
         <v>2026</v>
@@ -7039,10 +7035,10 @@
         <v>101</v>
       </c>
       <c r="C297" s="3">
-        <v>30.79</v>
+        <v>32.28</v>
       </c>
       <c r="D297" s="6">
-        <v>36.79</v>
+        <v>38.53</v>
       </c>
       <c r="E297">
         <v>2026</v>
@@ -7059,10 +7055,10 @@
         <v>102</v>
       </c>
       <c r="C298" s="3">
-        <v>17.41</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="D298" s="6">
-        <v>21.37</v>
+        <v>23.81</v>
       </c>
       <c r="E298">
         <v>2026</v>
@@ -7079,10 +7075,10 @@
         <v>103</v>
       </c>
       <c r="C299" s="3">
-        <v>51.61</v>
+        <v>46.77</v>
       </c>
       <c r="D299" s="6">
-        <v>56.95</v>
+        <v>52.13</v>
       </c>
       <c r="E299">
         <v>2026</v>
@@ -7099,10 +7095,10 @@
         <v>104</v>
       </c>
       <c r="C300" s="3">
-        <v>41.89</v>
+        <v>42.62</v>
       </c>
       <c r="D300" s="6">
-        <v>46.03</v>
+        <v>47.24</v>
       </c>
       <c r="E300">
         <v>2026</v>
@@ -7119,10 +7115,10 @@
         <v>105</v>
       </c>
       <c r="C301" s="3">
-        <v>46.29</v>
+        <v>45.24</v>
       </c>
       <c r="D301" s="6">
-        <v>50.88</v>
+        <v>50.36</v>
       </c>
       <c r="E301">
         <v>2026</v>
@@ -7139,10 +7135,10 @@
         <v>106</v>
       </c>
       <c r="C302" s="3">
-        <v>243.69</v>
+        <v>228.54</v>
       </c>
       <c r="D302" s="6">
-        <v>282.92</v>
+        <v>268.5</v>
       </c>
       <c r="E302">
         <v>2026</v>
@@ -7159,10 +7155,10 @@
         <v>107</v>
       </c>
       <c r="C303" s="3">
-        <v>22.07</v>
+        <v>29.06</v>
       </c>
       <c r="D303" s="6">
-        <v>28</v>
+        <v>36.9</v>
       </c>
       <c r="E303">
         <v>2026</v>
@@ -7179,10 +7175,10 @@
         <v>108</v>
       </c>
       <c r="C304" s="3">
-        <v>36.869999999999997</v>
+        <v>37</v>
       </c>
       <c r="D304" s="6">
-        <v>42.02</v>
+        <v>42.33</v>
       </c>
       <c r="E304">
         <v>2026</v>
@@ -7199,10 +7195,10 @@
         <v>109</v>
       </c>
       <c r="C305" s="3">
-        <v>50.26</v>
+        <v>49.07</v>
       </c>
       <c r="D305" s="6">
-        <v>55.33</v>
+        <v>54.39</v>
       </c>
       <c r="E305">
         <v>2026</v>
@@ -7219,10 +7215,10 @@
         <v>110</v>
       </c>
       <c r="C306" s="3">
-        <v>44.19</v>
+        <v>57.87</v>
       </c>
       <c r="D306" s="6">
-        <v>50.62</v>
+        <v>66.3</v>
       </c>
       <c r="E306">
         <v>2026</v>
@@ -7239,10 +7235,10 @@
         <v>111</v>
       </c>
       <c r="C307" s="3">
-        <v>48.64</v>
+        <v>44.86</v>
       </c>
       <c r="D307" s="6">
-        <v>54.4</v>
+        <v>50.59</v>
       </c>
       <c r="E307">
         <v>2026</v>
@@ -7259,10 +7255,10 @@
         <v>112</v>
       </c>
       <c r="C308" s="3">
-        <v>141.9</v>
+        <v>141.87</v>
       </c>
       <c r="D308" s="6">
-        <v>180.62</v>
+        <v>180.59</v>
       </c>
       <c r="E308">
         <v>2026</v>
@@ -7279,10 +7275,10 @@
         <v>113</v>
       </c>
       <c r="C309" s="3">
-        <v>46.57</v>
+        <v>46.51</v>
       </c>
       <c r="D309" s="6">
-        <v>53.71</v>
+        <v>54.68</v>
       </c>
       <c r="E309">
         <v>2026</v>
@@ -7299,10 +7295,10 @@
         <v>114</v>
       </c>
       <c r="C310" s="3">
-        <v>67.7</v>
+        <v>69.23</v>
       </c>
       <c r="D310" s="6">
-        <v>75.77</v>
+        <v>78.36</v>
       </c>
       <c r="E310">
         <v>2026</v>
@@ -7319,10 +7315,10 @@
         <v>115</v>
       </c>
       <c r="C311" s="3">
-        <v>45.38</v>
+        <v>61.02</v>
       </c>
       <c r="D311" s="6">
-        <v>54.7</v>
+        <v>74.16</v>
       </c>
       <c r="E311">
         <v>2026</v>
@@ -7339,10 +7335,10 @@
         <v>116</v>
       </c>
       <c r="C312" s="3">
-        <v>29.36</v>
+        <v>28.16</v>
       </c>
       <c r="D312" s="6">
-        <v>33.21</v>
+        <v>32.15</v>
       </c>
       <c r="E312">
         <v>2026</v>
@@ -7359,10 +7355,10 @@
         <v>117</v>
       </c>
       <c r="C313" s="3">
-        <v>43.12</v>
+        <v>53.95</v>
       </c>
       <c r="D313" s="6">
-        <v>52.51</v>
+        <v>65.819999999999993</v>
       </c>
       <c r="E313">
         <v>2026</v>
@@ -7379,10 +7375,10 @@
         <v>118</v>
       </c>
       <c r="C314" s="3">
-        <v>64.349999999999994</v>
+        <v>66.95</v>
       </c>
       <c r="D314" s="6">
-        <v>70.459999999999994</v>
+        <v>73.84</v>
       </c>
       <c r="E314">
         <v>2026</v>
@@ -7399,10 +7395,10 @@
         <v>119</v>
       </c>
       <c r="C315" s="3">
-        <v>28.07</v>
+        <v>25.97</v>
       </c>
       <c r="D315" s="6">
-        <v>31.67</v>
+        <v>29.58</v>
       </c>
       <c r="E315">
         <v>2026</v>
@@ -7419,10 +7415,10 @@
         <v>120</v>
       </c>
       <c r="C316" s="3">
-        <v>32.869999999999997</v>
+        <v>30.09</v>
       </c>
       <c r="D316" s="6">
-        <v>36.33</v>
+        <v>33.770000000000003</v>
       </c>
       <c r="E316">
         <v>2026</v>
@@ -7439,10 +7435,10 @@
         <v>121</v>
       </c>
       <c r="C317" s="3">
-        <v>32.22</v>
+        <v>28.87</v>
       </c>
       <c r="D317" s="6">
-        <v>35.39</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="E317">
         <v>2026</v>
@@ -7459,10 +7455,10 @@
         <v>122</v>
       </c>
       <c r="C318" s="3">
-        <v>54.24</v>
+        <v>55.12</v>
       </c>
       <c r="D318" s="6">
-        <v>60.92</v>
+        <v>63.29</v>
       </c>
       <c r="E318">
         <v>2026</v>
@@ -7479,10 +7475,10 @@
         <v>123</v>
       </c>
       <c r="C319" s="3">
-        <v>37.25</v>
+        <v>32.19</v>
       </c>
       <c r="D319" s="6">
-        <v>40.44</v>
+        <v>35.44</v>
       </c>
       <c r="E319">
         <v>2026</v>
@@ -7499,10 +7495,10 @@
         <v>124</v>
       </c>
       <c r="C320" s="3">
-        <v>101.53</v>
+        <v>91.14</v>
       </c>
       <c r="D320" s="6">
-        <v>106.7</v>
+        <v>97.52</v>
       </c>
       <c r="E320">
         <v>2026</v>
@@ -7519,10 +7515,10 @@
         <v>125</v>
       </c>
       <c r="C321" s="3">
-        <v>17.739999999999998</v>
+        <v>23.89</v>
       </c>
       <c r="D321" s="6">
-        <v>21.94</v>
+        <v>29.51</v>
       </c>
       <c r="E321">
         <v>2026</v>
@@ -7539,10 +7535,10 @@
         <v>126</v>
       </c>
       <c r="C322" s="3">
-        <v>18.14</v>
+        <v>22.95</v>
       </c>
       <c r="D322" s="6">
-        <v>22.24</v>
+        <v>28.15</v>
       </c>
       <c r="E322">
         <v>2026</v>
@@ -7559,10 +7555,10 @@
         <v>127</v>
       </c>
       <c r="C323" s="3">
-        <v>19.23</v>
+        <v>27.26</v>
       </c>
       <c r="D323" s="6">
-        <v>23.72</v>
+        <v>33.630000000000003</v>
       </c>
       <c r="E323">
         <v>2026</v>
@@ -7579,10 +7575,10 @@
         <v>128</v>
       </c>
       <c r="C324" s="3">
-        <v>22.2</v>
+        <v>28.58</v>
       </c>
       <c r="D324" s="6">
-        <v>27.08</v>
+        <v>34.85</v>
       </c>
       <c r="E324">
         <v>2026</v>
@@ -7599,10 +7595,10 @@
         <v>129</v>
       </c>
       <c r="C325" s="3">
-        <v>38.450000000000003</v>
+        <v>41.55</v>
       </c>
       <c r="D325" s="6">
-        <v>45.2</v>
+        <v>48.97</v>
       </c>
       <c r="E325">
         <v>2026</v>
@@ -7619,10 +7615,10 @@
         <v>130</v>
       </c>
       <c r="C326" s="3">
-        <v>25.7</v>
+        <v>38.42</v>
       </c>
       <c r="D326" s="6">
-        <v>30.96</v>
+        <v>46.32</v>
       </c>
       <c r="E326">
         <v>2026</v>
@@ -7639,10 +7635,10 @@
         <v>131</v>
       </c>
       <c r="C327" s="3">
-        <v>22.63</v>
+        <v>31.2</v>
       </c>
       <c r="D327" s="6">
-        <v>27.34</v>
+        <v>37.700000000000003</v>
       </c>
       <c r="E327">
         <v>2026</v>
@@ -7659,10 +7655,10 @@
         <v>132</v>
       </c>
       <c r="C328" s="3">
-        <v>30.12</v>
+        <v>35.21</v>
       </c>
       <c r="D328" s="6">
-        <v>35.770000000000003</v>
+        <v>41.97</v>
       </c>
       <c r="E328">
         <v>2026</v>
@@ -7679,10 +7675,10 @@
         <v>133</v>
       </c>
       <c r="C329" s="3">
-        <v>22.09</v>
+        <v>29.58</v>
       </c>
       <c r="D329" s="6">
-        <v>27.26</v>
+        <v>36.43</v>
       </c>
       <c r="E329">
         <v>2026</v>
@@ -7699,10 +7695,10 @@
         <v>134</v>
       </c>
       <c r="C330" s="3">
-        <v>5.74</v>
+        <v>54.45</v>
       </c>
       <c r="D330" s="6">
-        <v>7.32</v>
+        <v>69.48</v>
       </c>
       <c r="E330">
         <v>2026</v>
@@ -7719,10 +7715,10 @@
         <v>135</v>
       </c>
       <c r="C331" s="3">
-        <v>31.09</v>
+        <v>38.79</v>
       </c>
       <c r="D331" s="6">
-        <v>36.909999999999997</v>
+        <v>45.81</v>
       </c>
       <c r="E331">
         <v>2026</v>
@@ -7739,10 +7735,10 @@
         <v>136</v>
       </c>
       <c r="C332" s="3">
-        <v>20.41</v>
+        <v>30.55</v>
       </c>
       <c r="D332" s="6">
-        <v>25.4</v>
+        <v>37.880000000000003</v>
       </c>
       <c r="E332">
         <v>2026</v>
@@ -7759,10 +7755,10 @@
         <v>137</v>
       </c>
       <c r="C333" s="3">
-        <v>66.209999999999994</v>
+        <v>60.12</v>
       </c>
       <c r="D333" s="6">
-        <v>71.680000000000007</v>
+        <v>66.08</v>
       </c>
       <c r="E333">
         <v>2026</v>
@@ -7779,10 +7775,10 @@
         <v>138</v>
       </c>
       <c r="C334" s="3">
-        <v>33.51</v>
+        <v>34.61</v>
       </c>
       <c r="D334" s="6">
-        <v>37.69</v>
+        <v>39.369999999999997</v>
       </c>
       <c r="E334">
         <v>2026</v>
@@ -7799,10 +7795,10 @@
         <v>139</v>
       </c>
       <c r="C335" s="3">
-        <v>35.020000000000003</v>
+        <v>41</v>
       </c>
       <c r="D335" s="6">
-        <v>41.07</v>
+        <v>48.15</v>
       </c>
       <c r="E335">
         <v>2026</v>
@@ -7819,10 +7815,10 @@
         <v>140</v>
       </c>
       <c r="C336" s="3">
-        <v>13.96</v>
+        <v>15.46</v>
       </c>
       <c r="D336" s="6">
-        <v>17.18</v>
+        <v>19.059999999999999</v>
       </c>
       <c r="E336">
         <v>2026</v>
@@ -7839,10 +7835,10 @@
         <v>141</v>
       </c>
       <c r="C337" s="3">
-        <v>13.22</v>
+        <v>15.02</v>
       </c>
       <c r="D337" s="6">
-        <v>15.89</v>
+        <v>18.11</v>
       </c>
       <c r="E337">
         <v>2026</v>
@@ -7859,10 +7855,10 @@
         <v>142</v>
       </c>
       <c r="C338" s="3">
-        <v>22.3</v>
+        <v>32.89</v>
       </c>
       <c r="D338" s="6">
-        <v>27.85</v>
+        <v>40.950000000000003</v>
       </c>
       <c r="E338">
         <v>2026</v>
@@ -7879,10 +7875,10 @@
         <v>143</v>
       </c>
       <c r="C339" s="3">
-        <v>29.7</v>
+        <v>47.21</v>
       </c>
       <c r="D339" s="6">
-        <v>37.86</v>
+        <v>60.16</v>
       </c>
       <c r="E339">
         <v>2026</v>
@@ -7899,10 +7895,10 @@
         <v>144</v>
       </c>
       <c r="C340" s="3">
-        <v>14.76</v>
+        <v>31.78</v>
       </c>
       <c r="D340" s="6">
-        <v>18.36</v>
+        <v>39.630000000000003</v>
       </c>
       <c r="E340">
         <v>2026</v>
@@ -7919,10 +7915,10 @@
         <v>145</v>
       </c>
       <c r="C341" s="3">
-        <v>21.06</v>
+        <v>38</v>
       </c>
       <c r="D341" s="6">
-        <v>26.19</v>
+        <v>47.26</v>
       </c>
       <c r="E341">
         <v>2026</v>
@@ -7939,10 +7935,10 @@
         <v>146</v>
       </c>
       <c r="C342" s="3">
-        <v>17.5</v>
+        <v>32.020000000000003</v>
       </c>
       <c r="D342" s="6">
-        <v>22.23</v>
+        <v>40.64</v>
       </c>
       <c r="E342">
         <v>2026</v>
@@ -7959,10 +7955,10 @@
         <v>147</v>
       </c>
       <c r="C343" s="3">
-        <v>17.670000000000002</v>
+        <v>27.48</v>
       </c>
       <c r="D343" s="6">
-        <v>21.71</v>
+        <v>33.79</v>
       </c>
       <c r="E343">
         <v>2026</v>
@@ -7979,10 +7975,10 @@
         <v>148</v>
       </c>
       <c r="C344" s="3">
-        <v>17.53</v>
+        <v>20.9</v>
       </c>
       <c r="D344" s="6">
-        <v>20.84</v>
+        <v>24.82</v>
       </c>
       <c r="E344">
         <v>2026</v>
@@ -7999,10 +7995,10 @@
         <v>149</v>
       </c>
       <c r="C345" s="3">
-        <v>28.49</v>
+        <v>34.25</v>
       </c>
       <c r="D345" s="6">
-        <v>33.97</v>
+        <v>40.909999999999997</v>
       </c>
       <c r="E345">
         <v>2026</v>
@@ -8019,10 +8015,10 @@
         <v>150</v>
       </c>
       <c r="C346" s="3">
-        <v>22.15</v>
+        <v>24.58</v>
       </c>
       <c r="D346" s="6">
-        <v>26.72</v>
+        <v>29.67</v>
       </c>
       <c r="E346">
         <v>2026</v>
@@ -8039,10 +8035,10 @@
         <v>151</v>
       </c>
       <c r="C347" s="3">
-        <v>21.48</v>
+        <v>22.62</v>
       </c>
       <c r="D347" s="6">
-        <v>24.61</v>
+        <v>25.93</v>
       </c>
       <c r="E347">
         <v>2026</v>
@@ -8059,10 +8055,10 @@
         <v>152</v>
       </c>
       <c r="C348" s="3">
-        <v>24.12</v>
+        <v>29.3</v>
       </c>
       <c r="D348" s="6">
-        <v>29.42</v>
+        <v>35.76</v>
       </c>
       <c r="E348">
         <v>2026</v>
@@ -8079,10 +8075,10 @@
         <v>153</v>
       </c>
       <c r="C349" s="3">
-        <v>19.16</v>
+        <v>27.34</v>
       </c>
       <c r="D349" s="6">
-        <v>24.04</v>
+        <v>34.36</v>
       </c>
       <c r="E349">
         <v>2026</v>
@@ -8099,10 +8095,10 @@
         <v>154</v>
       </c>
       <c r="C350" s="3">
-        <v>11.11</v>
+        <v>14.47</v>
       </c>
       <c r="D350" s="6">
-        <v>14.08</v>
+        <v>18.34</v>
       </c>
       <c r="E350">
         <v>2026</v>
@@ -8119,10 +8115,10 @@
         <v>155</v>
       </c>
       <c r="C351" s="3">
-        <v>12.35</v>
+        <v>12.36</v>
       </c>
       <c r="D351" s="6">
-        <v>14.83</v>
+        <v>14.85</v>
       </c>
       <c r="E351">
         <v>2026</v>
@@ -8139,10 +8135,10 @@
         <v>156</v>
       </c>
       <c r="C352" s="3">
-        <v>21.04</v>
+        <v>20.99</v>
       </c>
       <c r="D352" s="6">
-        <v>25.54</v>
+        <v>25.46</v>
       </c>
       <c r="E352">
         <v>2026</v>
@@ -8159,10 +8155,10 @@
         <v>157</v>
       </c>
       <c r="C353" s="3">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="D353" s="6">
-        <v>26.88</v>
+        <v>26.62</v>
       </c>
       <c r="E353">
         <v>2026</v>
@@ -8179,10 +8175,10 @@
         <v>158</v>
       </c>
       <c r="C354" s="3">
-        <v>11.73</v>
+        <v>11.69</v>
       </c>
       <c r="D354" s="6">
-        <v>14.94</v>
+        <v>14.89</v>
       </c>
       <c r="E354">
         <v>2026</v>
@@ -8199,10 +8195,10 @@
         <v>159</v>
       </c>
       <c r="C355" s="3">
-        <v>14.34</v>
+        <v>15.2</v>
       </c>
       <c r="D355" s="6">
-        <v>17.38</v>
+        <v>18.440000000000001</v>
       </c>
       <c r="E355">
         <v>2026</v>
@@ -8219,10 +8215,10 @@
         <v>160</v>
       </c>
       <c r="C356" s="3">
-        <v>22.24</v>
+        <v>28.66</v>
       </c>
       <c r="D356" s="6">
-        <v>27.41</v>
+        <v>35.33</v>
       </c>
       <c r="E356">
         <v>2026</v>
@@ -8239,10 +8235,10 @@
         <v>161</v>
       </c>
       <c r="C357" s="3">
-        <v>14.91</v>
+        <v>19.45</v>
       </c>
       <c r="D357" s="6">
-        <v>18.899999999999999</v>
+        <v>24.66</v>
       </c>
       <c r="E357">
         <v>2026</v>
@@ -8259,10 +8255,10 @@
         <v>162</v>
       </c>
       <c r="C358" s="3">
-        <v>31.16</v>
+        <v>26.91</v>
       </c>
       <c r="D358" s="6">
-        <v>34.94</v>
+        <v>30.74</v>
       </c>
       <c r="E358">
         <v>2026</v>
@@ -8279,10 +8275,10 @@
         <v>163</v>
       </c>
       <c r="C359" s="3">
-        <v>28.83</v>
+        <v>44.41</v>
       </c>
       <c r="D359" s="6">
-        <v>36.479999999999997</v>
+        <v>56.11</v>
       </c>
       <c r="E359">
         <v>2026</v>
@@ -8299,10 +8295,10 @@
         <v>164</v>
       </c>
       <c r="C360" s="3">
-        <v>28.01</v>
+        <v>43.56</v>
       </c>
       <c r="D360" s="6">
-        <v>35.17</v>
+        <v>54.66</v>
       </c>
       <c r="E360">
         <v>2026</v>
@@ -8319,10 +8315,10 @@
         <v>165</v>
       </c>
       <c r="C361" s="3">
-        <v>23.18</v>
+        <v>28.98</v>
       </c>
       <c r="D361" s="6">
-        <v>28.26</v>
+        <v>35.15</v>
       </c>
       <c r="E361">
         <v>2026</v>
@@ -8339,10 +8335,10 @@
         <v>166</v>
       </c>
       <c r="C362" s="3">
-        <v>30</v>
+        <v>34.229999999999997</v>
       </c>
       <c r="D362" s="6">
-        <v>36.950000000000003</v>
+        <v>42.06</v>
       </c>
       <c r="E362">
         <v>2026</v>
@@ -8359,10 +8355,10 @@
         <v>167</v>
       </c>
       <c r="C363" s="3">
-        <v>20.3</v>
+        <v>24.42</v>
       </c>
       <c r="D363" s="6">
-        <v>24.52</v>
+        <v>29.49</v>
       </c>
       <c r="E363">
         <v>2026</v>
@@ -8379,10 +8375,10 @@
         <v>168</v>
       </c>
       <c r="C364" s="3">
-        <v>23.69</v>
+        <v>27.44</v>
       </c>
       <c r="D364" s="6">
-        <v>29.38</v>
+        <v>34.01</v>
       </c>
       <c r="E364">
         <v>2026</v>
@@ -8399,10 +8395,10 @@
         <v>169</v>
       </c>
       <c r="C365" s="3">
-        <v>27.5</v>
+        <v>42.95</v>
       </c>
       <c r="D365" s="6">
-        <v>33.369999999999997</v>
+        <v>52.09</v>
       </c>
       <c r="E365">
         <v>2026</v>
@@ -8419,10 +8415,10 @@
         <v>170</v>
       </c>
       <c r="C366" s="3">
-        <v>31.15</v>
+        <v>33.909999999999997</v>
       </c>
       <c r="D366" s="6">
-        <v>39.68</v>
+        <v>43.12</v>
       </c>
       <c r="E366">
         <v>2026</v>
@@ -8439,10 +8435,10 @@
         <v>171</v>
       </c>
       <c r="C367" s="3">
-        <v>12.61</v>
+        <v>20.88</v>
       </c>
       <c r="D367" s="6">
-        <v>15.82</v>
+        <v>26.18</v>
       </c>
       <c r="E367">
         <v>2026</v>
@@ -8459,10 +8455,10 @@
         <v>172</v>
       </c>
       <c r="C368" s="3">
-        <v>13.98</v>
+        <v>20.14</v>
       </c>
       <c r="D368" s="6">
-        <v>17.22</v>
+        <v>24.8</v>
       </c>
       <c r="E368">
         <v>2026</v>
@@ -8479,10 +8475,10 @@
         <v>173</v>
       </c>
       <c r="C369" s="3">
-        <v>15.18</v>
+        <v>21.73</v>
       </c>
       <c r="D369" s="6">
-        <v>18.82</v>
+        <v>26.87</v>
       </c>
       <c r="E369">
         <v>2026</v>
@@ -8499,10 +8495,10 @@
         <v>174</v>
       </c>
       <c r="C370" s="3">
-        <v>13.46</v>
+        <v>18.190000000000001</v>
       </c>
       <c r="D370" s="6">
-        <v>16.98</v>
+        <v>22.93</v>
       </c>
       <c r="E370">
         <v>2026</v>
@@ -8519,10 +8515,10 @@
         <v>175</v>
       </c>
       <c r="C371" s="3">
-        <v>11.55</v>
+        <v>20.98</v>
       </c>
       <c r="D371" s="6">
-        <v>14.6</v>
+        <v>26.51</v>
       </c>
       <c r="E371">
         <v>2026</v>
@@ -8539,10 +8535,10 @@
         <v>176</v>
       </c>
       <c r="C372" s="3">
-        <v>12.98</v>
+        <v>16.57</v>
       </c>
       <c r="D372" s="6">
-        <v>16.38</v>
+        <v>20.89</v>
       </c>
       <c r="E372">
         <v>2026</v>
@@ -8559,10 +8555,10 @@
         <v>177</v>
       </c>
       <c r="C373" s="3">
-        <v>26.37</v>
+        <v>30.36</v>
       </c>
       <c r="D373" s="6">
-        <v>32.86</v>
+        <v>37.840000000000003</v>
       </c>
       <c r="E373">
         <v>2026</v>
@@ -8579,10 +8575,10 @@
         <v>178</v>
       </c>
       <c r="C374" s="3">
-        <v>26.26</v>
+        <v>37.119999999999997</v>
       </c>
       <c r="D374" s="6">
-        <v>32.479999999999997</v>
+        <v>45.97</v>
       </c>
       <c r="E374">
         <v>2026</v>
@@ -8599,10 +8595,10 @@
         <v>179</v>
       </c>
       <c r="C375" s="3">
-        <v>30.06</v>
+        <v>38.93</v>
       </c>
       <c r="D375" s="6">
-        <v>35.53</v>
+        <v>46.03</v>
       </c>
       <c r="E375">
         <v>2026</v>
@@ -8619,10 +8615,10 @@
         <v>180</v>
       </c>
       <c r="C376" s="3">
-        <v>17.940000000000001</v>
+        <v>45.31</v>
       </c>
       <c r="D376" s="6">
-        <v>22.91</v>
+        <v>57.85</v>
       </c>
       <c r="E376">
         <v>2026</v>
@@ -8639,10 +8635,10 @@
         <v>181</v>
       </c>
       <c r="C377" s="3">
-        <v>25.66</v>
+        <v>42.43</v>
       </c>
       <c r="D377" s="6">
-        <v>32.770000000000003</v>
+        <v>54.19</v>
       </c>
       <c r="E377">
         <v>2026</v>
@@ -8659,10 +8655,10 @@
         <v>182</v>
       </c>
       <c r="C378" s="3">
-        <v>41.9</v>
+        <v>39.35</v>
       </c>
       <c r="D378" s="6">
-        <v>47.8</v>
+        <v>45.71</v>
       </c>
       <c r="E378">
         <v>2026</v>
@@ -8679,10 +8675,10 @@
         <v>183</v>
       </c>
       <c r="C379" s="3">
-        <v>26.12</v>
+        <v>41.89</v>
       </c>
       <c r="D379" s="6">
-        <v>32.51</v>
+        <v>52.24</v>
       </c>
       <c r="E379">
         <v>2026</v>
@@ -8699,10 +8695,10 @@
         <v>184</v>
       </c>
       <c r="C380" s="3">
-        <v>27.68</v>
+        <v>45.09</v>
       </c>
       <c r="D380" s="6">
-        <v>34.83</v>
+        <v>56.73</v>
       </c>
       <c r="E380">
         <v>2026</v>
@@ -8719,10 +8715,10 @@
         <v>185</v>
       </c>
       <c r="C381" s="3">
-        <v>32.17</v>
+        <v>37.31</v>
       </c>
       <c r="D381" s="6">
-        <v>37.64</v>
+        <v>43.76</v>
       </c>
       <c r="E381">
         <v>2026</v>
@@ -8739,10 +8735,10 @@
         <v>186</v>
       </c>
       <c r="C382" s="3">
-        <v>64.650000000000006</v>
+        <v>62.55</v>
       </c>
       <c r="D382" s="6">
-        <v>72.75</v>
+        <v>71.77</v>
       </c>
       <c r="E382">
         <v>2026</v>
@@ -8759,10 +8755,10 @@
         <v>187</v>
       </c>
       <c r="C383" s="3">
-        <v>49.41</v>
+        <v>53.08</v>
       </c>
       <c r="D383" s="6">
-        <v>55.19</v>
+        <v>59.97</v>
       </c>
       <c r="E383">
         <v>2026</v>
@@ -8779,10 +8775,10 @@
         <v>188</v>
       </c>
       <c r="C384" s="3">
-        <v>34.299999999999997</v>
+        <v>41.07</v>
       </c>
       <c r="D384" s="6">
-        <v>42.1</v>
+        <v>50.37</v>
       </c>
       <c r="E384">
         <v>2026</v>
@@ -8799,10 +8795,10 @@
         <v>189</v>
       </c>
       <c r="C385" s="3">
-        <v>128.19</v>
+        <v>128.55000000000001</v>
       </c>
       <c r="D385" s="6">
-        <v>165.79</v>
+        <v>166.15</v>
       </c>
       <c r="E385">
         <v>2026</v>
@@ -8819,10 +8815,10 @@
         <v>190</v>
       </c>
       <c r="C386" s="3">
-        <v>19.53</v>
+        <v>33.97</v>
       </c>
       <c r="D386" s="6">
-        <v>23.91</v>
+        <v>41.59</v>
       </c>
       <c r="E386">
         <v>2026</v>
@@ -8839,10 +8835,10 @@
         <v>191</v>
       </c>
       <c r="C387" s="3">
-        <v>20.14</v>
+        <v>24.38</v>
       </c>
       <c r="D387" s="6">
-        <v>24.99</v>
+        <v>30.21</v>
       </c>
       <c r="E387">
         <v>2026</v>
@@ -8859,10 +8855,10 @@
         <v>192</v>
       </c>
       <c r="C388" s="3">
-        <v>17.87</v>
+        <v>21.41</v>
       </c>
       <c r="D388" s="6">
-        <v>22.64</v>
+        <v>27.13</v>
       </c>
       <c r="E388">
         <v>2026</v>
@@ -8879,10 +8875,10 @@
         <v>193</v>
       </c>
       <c r="C389" s="3">
-        <v>25.04</v>
+        <v>32</v>
       </c>
       <c r="D389" s="6">
-        <v>29.56</v>
+        <v>37.9</v>
       </c>
       <c r="E389">
         <v>2026</v>
@@ -8899,10 +8895,10 @@
         <v>194</v>
       </c>
       <c r="C390" s="3">
-        <v>34.06</v>
+        <v>33.799999999999997</v>
       </c>
       <c r="D390" s="6">
-        <v>37.42</v>
+        <v>37.14</v>
       </c>
       <c r="E390">
         <v>2026</v>
@@ -8919,10 +8915,10 @@
         <v>195</v>
       </c>
       <c r="C391" s="3">
-        <v>15.23</v>
+        <v>30.24</v>
       </c>
       <c r="D391" s="6">
-        <v>19.14</v>
+        <v>38</v>
       </c>
       <c r="E391">
         <v>2026</v>
@@ -8939,10 +8935,10 @@
         <v>196</v>
       </c>
       <c r="C392" s="3">
-        <v>15.88</v>
+        <v>35.770000000000003</v>
       </c>
       <c r="D392" s="6">
-        <v>19.98</v>
+        <v>45.03</v>
       </c>
       <c r="E392">
         <v>2026</v>
@@ -8959,10 +8955,10 @@
         <v>197</v>
       </c>
       <c r="C393" s="3">
-        <v>39.89</v>
+        <v>35.61</v>
       </c>
       <c r="D393" s="6">
-        <v>44.65</v>
+        <v>40.479999999999997</v>
       </c>
       <c r="E393">
         <v>2026</v>
@@ -8979,10 +8975,10 @@
         <v>198</v>
       </c>
       <c r="C394" s="3">
-        <v>23.05</v>
+        <v>22.28</v>
       </c>
       <c r="D394" s="6">
-        <v>26.89</v>
+        <v>26.28</v>
       </c>
       <c r="E394">
         <v>2026</v>
@@ -8999,10 +8995,10 @@
         <v>199</v>
       </c>
       <c r="C395" s="3">
-        <v>13.72</v>
+        <v>17.309999999999999</v>
       </c>
       <c r="D395" s="6">
-        <v>17.2</v>
+        <v>21.72</v>
       </c>
       <c r="E395">
         <v>2026</v>
@@ -9019,10 +9015,10 @@
         <v>200</v>
       </c>
       <c r="C396" s="3">
-        <v>39.32</v>
+        <v>38.36</v>
       </c>
       <c r="D396" s="6">
-        <v>44.11</v>
+        <v>43.71</v>
       </c>
       <c r="E396">
         <v>2026</v>
@@ -9039,10 +9035,10 @@
         <v>201</v>
       </c>
       <c r="C397" s="3">
-        <v>15.84</v>
+        <v>22.37</v>
       </c>
       <c r="D397" s="6">
-        <v>19.64</v>
+        <v>27.77</v>
       </c>
       <c r="E397">
         <v>2026</v>
@@ -9059,10 +9055,10 @@
         <v>202</v>
       </c>
       <c r="C398" s="3">
-        <v>20.81</v>
+        <v>31.38</v>
       </c>
       <c r="D398" s="6">
-        <v>25.09</v>
+        <v>37.89</v>
       </c>
       <c r="E398">
         <v>2026</v>
@@ -9079,10 +9075,10 @@
         <v>203</v>
       </c>
       <c r="C399" s="3">
-        <v>32</v>
+        <v>31.64</v>
       </c>
       <c r="D399" s="6">
-        <v>35.61</v>
+        <v>35.450000000000003</v>
       </c>
       <c r="E399">
         <v>2026</v>
@@ -9099,10 +9095,10 @@
         <v>204</v>
       </c>
       <c r="C400" s="3">
-        <v>22.13</v>
+        <v>20.79</v>
       </c>
       <c r="D400" s="6">
-        <v>25.69</v>
+        <v>24.37</v>
       </c>
       <c r="E400">
         <v>2026</v>
@@ -9119,10 +9115,10 @@
         <v>202</v>
       </c>
       <c r="C401" s="3">
-        <v>20.81</v>
+        <v>31.38</v>
       </c>
       <c r="D401" s="6">
-        <v>25.09</v>
+        <v>37.89</v>
       </c>
       <c r="E401">
         <v>2026</v>
@@ -9139,10 +9135,10 @@
         <v>6</v>
       </c>
       <c r="C402" s="3">
-        <v>23.76</v>
+        <v>34.020000000000003</v>
       </c>
       <c r="D402" s="6">
-        <v>28.85</v>
+        <v>41.32</v>
       </c>
       <c r="E402">
         <v>2026</v>
@@ -9159,10 +9155,10 @@
         <v>7</v>
       </c>
       <c r="C403" s="3">
-        <v>26.39</v>
+        <v>40.950000000000003</v>
       </c>
       <c r="D403" s="6">
-        <v>32.44</v>
+        <v>50.32</v>
       </c>
       <c r="E403">
         <v>2026</v>
@@ -9179,10 +9175,10 @@
         <v>8</v>
       </c>
       <c r="C404" s="3">
-        <v>23.31</v>
+        <v>28.45</v>
       </c>
       <c r="D404" s="6">
-        <v>28.08</v>
+        <v>34.26</v>
       </c>
       <c r="E404">
         <v>2026</v>
@@ -9219,10 +9215,10 @@
         <v>10</v>
       </c>
       <c r="C406" s="3">
-        <v>37.340000000000003</v>
+        <v>39.4</v>
       </c>
       <c r="D406" s="6">
-        <v>41.9</v>
+        <v>44.37</v>
       </c>
       <c r="E406">
         <v>2026</v>
@@ -9239,10 +9235,10 @@
         <v>11</v>
       </c>
       <c r="C407" s="3">
-        <v>36.1</v>
+        <v>37.92</v>
       </c>
       <c r="D407" s="6">
-        <v>40.03</v>
+        <v>42.16</v>
       </c>
       <c r="E407">
         <v>2026</v>
@@ -9299,10 +9295,10 @@
         <v>14</v>
       </c>
       <c r="C410" s="3">
-        <v>19.850000000000001</v>
+        <v>23.89</v>
       </c>
       <c r="D410" s="6">
-        <v>24.31</v>
+        <v>29.24</v>
       </c>
       <c r="E410">
         <v>2026</v>
@@ -9319,10 +9315,10 @@
         <v>15</v>
       </c>
       <c r="C411" s="3">
-        <v>24.82</v>
+        <v>30.79</v>
       </c>
       <c r="D411" s="6">
-        <v>29.72</v>
+        <v>36.86</v>
       </c>
       <c r="E411">
         <v>2026</v>
@@ -9339,10 +9335,10 @@
         <v>16</v>
       </c>
       <c r="C412" s="3">
-        <v>35.200000000000003</v>
+        <v>63.06</v>
       </c>
       <c r="D412" s="6">
-        <v>43.63</v>
+        <v>78.14</v>
       </c>
       <c r="E412">
         <v>2026</v>
@@ -9359,10 +9355,10 @@
         <v>17</v>
       </c>
       <c r="C413" s="3">
-        <v>26.64</v>
+        <v>27.53</v>
       </c>
       <c r="D413" s="6">
-        <v>29.91</v>
+        <v>30.97</v>
       </c>
       <c r="E413">
         <v>2026</v>
@@ -9379,10 +9375,10 @@
         <v>18</v>
       </c>
       <c r="C414" s="3">
-        <v>22.84</v>
+        <v>23.12</v>
       </c>
       <c r="D414" s="6">
-        <v>25.75</v>
+        <v>26.08</v>
       </c>
       <c r="E414">
         <v>2026</v>
@@ -9399,10 +9395,10 @@
         <v>19</v>
       </c>
       <c r="C415" s="3">
-        <v>17.66</v>
+        <v>18.05</v>
       </c>
       <c r="D415" s="6">
-        <v>21.61</v>
+        <v>22.1</v>
       </c>
       <c r="E415">
         <v>2026</v>
@@ -9419,10 +9415,10 @@
         <v>20</v>
       </c>
       <c r="C416" s="3">
-        <v>17.920000000000002</v>
+        <v>18.34</v>
       </c>
       <c r="D416" s="6">
-        <v>22.43</v>
+        <v>22.95</v>
       </c>
       <c r="E416">
         <v>2026</v>
@@ -9439,10 +9435,10 @@
         <v>21</v>
       </c>
       <c r="C417" s="3">
-        <v>12.42</v>
+        <v>12.81</v>
       </c>
       <c r="D417" s="6">
-        <v>15.08</v>
+        <v>15.56</v>
       </c>
       <c r="E417">
         <v>2026</v>
@@ -9459,10 +9455,10 @@
         <v>22</v>
       </c>
       <c r="C418" s="3">
-        <v>33.47</v>
+        <v>33.950000000000003</v>
       </c>
       <c r="D418" s="6">
-        <v>36.25</v>
+        <v>36.79</v>
       </c>
       <c r="E418">
         <v>2026</v>
@@ -9479,10 +9475,10 @@
         <v>23</v>
       </c>
       <c r="C419" s="3">
-        <v>36.659999999999997</v>
+        <v>36.869999999999997</v>
       </c>
       <c r="D419" s="6">
-        <v>39.96</v>
+        <v>40.200000000000003</v>
       </c>
       <c r="E419">
         <v>2026</v>
@@ -9499,10 +9495,10 @@
         <v>24</v>
       </c>
       <c r="C420" s="3">
-        <v>38.65</v>
+        <v>39.83</v>
       </c>
       <c r="D420" s="6">
-        <v>43.34</v>
+        <v>44.75</v>
       </c>
       <c r="E420">
         <v>2026</v>
@@ -9519,10 +9515,10 @@
         <v>25</v>
       </c>
       <c r="C421" s="3">
-        <v>46.82</v>
+        <v>47.16</v>
       </c>
       <c r="D421" s="6">
-        <v>51.14</v>
+        <v>51.54</v>
       </c>
       <c r="E421">
         <v>2026</v>
@@ -9539,10 +9535,10 @@
         <v>26</v>
       </c>
       <c r="C422" s="3">
-        <v>36.28</v>
+        <v>47.4</v>
       </c>
       <c r="D422" s="6">
-        <v>42.69</v>
+        <v>55.76</v>
       </c>
       <c r="E422">
         <v>2026</v>
@@ -9559,10 +9555,10 @@
         <v>27</v>
       </c>
       <c r="C423" s="3">
-        <v>23.25</v>
+        <v>36.130000000000003</v>
       </c>
       <c r="D423" s="6">
-        <v>28.33</v>
+        <v>44.02</v>
       </c>
       <c r="E423">
         <v>2026</v>
@@ -9579,10 +9575,10 @@
         <v>28</v>
       </c>
       <c r="C424" s="3">
-        <v>45.6</v>
+        <v>57.31</v>
       </c>
       <c r="D424" s="6">
-        <v>51.77</v>
+        <v>65.650000000000006</v>
       </c>
       <c r="E424">
         <v>2026</v>
@@ -9599,10 +9595,10 @@
         <v>29</v>
       </c>
       <c r="C425" s="3">
-        <v>37.18</v>
+        <v>49.84</v>
       </c>
       <c r="D425" s="6">
-        <v>43.41</v>
+        <v>59.12</v>
       </c>
       <c r="E425">
         <v>2026</v>
@@ -9619,10 +9615,10 @@
         <v>30</v>
       </c>
       <c r="C426" s="3">
-        <v>147.77000000000001</v>
+        <v>160.63</v>
       </c>
       <c r="D426" s="6">
-        <v>165</v>
+        <v>180.67</v>
       </c>
       <c r="E426">
         <v>2026</v>
@@ -9639,10 +9635,10 @@
         <v>31</v>
       </c>
       <c r="C427" s="3">
-        <v>24.61</v>
+        <v>29.41</v>
       </c>
       <c r="D427" s="6">
-        <v>29.93</v>
+        <v>35.770000000000003</v>
       </c>
       <c r="E427">
         <v>2026</v>
@@ -9659,10 +9655,10 @@
         <v>32</v>
       </c>
       <c r="C428" s="3">
-        <v>26.86</v>
+        <v>30.7</v>
       </c>
       <c r="D428" s="6">
-        <v>33.64</v>
+        <v>38.450000000000003</v>
       </c>
       <c r="E428">
         <v>2026</v>
@@ -9679,10 +9675,10 @@
         <v>33</v>
       </c>
       <c r="C429" s="3">
-        <v>40.31</v>
+        <v>43.49</v>
       </c>
       <c r="D429" s="6">
-        <v>47.49</v>
+        <v>51.42</v>
       </c>
       <c r="E429">
         <v>2026</v>
@@ -9699,10 +9695,10 @@
         <v>34</v>
       </c>
       <c r="C430" s="3">
-        <v>59.06</v>
+        <v>70.14</v>
       </c>
       <c r="D430" s="6">
-        <v>67.319999999999993</v>
+        <v>80.3</v>
       </c>
       <c r="E430">
         <v>2026</v>
@@ -9719,10 +9715,10 @@
         <v>35</v>
       </c>
       <c r="C431" s="3">
-        <v>42.37</v>
+        <v>43.73</v>
       </c>
       <c r="D431" s="6">
-        <v>48.55</v>
+        <v>50.19</v>
       </c>
       <c r="E431">
         <v>2026</v>
@@ -9739,10 +9735,10 @@
         <v>36</v>
       </c>
       <c r="C432" s="3">
-        <v>39.06</v>
+        <v>40.840000000000003</v>
       </c>
       <c r="D432" s="6">
-        <v>43.83</v>
+        <v>45.93</v>
       </c>
       <c r="E432">
         <v>2026</v>
@@ -9759,10 +9755,10 @@
         <v>37</v>
       </c>
       <c r="C433" s="3">
-        <v>38.049999999999997</v>
+        <v>39.39</v>
       </c>
       <c r="D433" s="6">
-        <v>42.34</v>
+        <v>43.93</v>
       </c>
       <c r="E433">
         <v>2026</v>
@@ -9779,10 +9775,10 @@
         <v>38</v>
       </c>
       <c r="C434" s="3">
-        <v>44.44</v>
+        <v>45.31</v>
       </c>
       <c r="D434" s="6">
-        <v>49.19</v>
+        <v>50.23</v>
       </c>
       <c r="E434">
         <v>2026</v>
@@ -9799,10 +9795,10 @@
         <v>39</v>
       </c>
       <c r="C435" s="3">
-        <v>20.64</v>
+        <v>30.01</v>
       </c>
       <c r="D435" s="6">
-        <v>25.02</v>
+        <v>36.369999999999997</v>
       </c>
       <c r="E435">
         <v>2026</v>
@@ -9819,10 +9815,10 @@
         <v>40</v>
       </c>
       <c r="C436" s="3">
-        <v>30.74</v>
+        <v>44.82</v>
       </c>
       <c r="D436" s="6">
-        <v>35.44</v>
+        <v>51.67</v>
       </c>
       <c r="E436">
         <v>2026</v>
@@ -9859,10 +9855,10 @@
         <v>42</v>
       </c>
       <c r="C438" s="3">
-        <v>14.16</v>
+        <v>19.7</v>
       </c>
       <c r="D438" s="6">
-        <v>17.829999999999998</v>
+        <v>24.82</v>
       </c>
       <c r="E438">
         <v>2026</v>
@@ -9879,10 +9875,10 @@
         <v>43</v>
       </c>
       <c r="C439" s="3">
-        <v>18.53</v>
+        <v>20.07</v>
       </c>
       <c r="D439" s="6">
-        <v>23.63</v>
+        <v>25.59</v>
       </c>
       <c r="E439">
         <v>2026</v>
@@ -9899,10 +9895,10 @@
         <v>44</v>
       </c>
       <c r="C440" s="3">
-        <v>24.53</v>
+        <v>36.479999999999997</v>
       </c>
       <c r="D440" s="6">
-        <v>30.56</v>
+        <v>45.45</v>
       </c>
       <c r="E440">
         <v>2026</v>
@@ -9919,10 +9915,10 @@
         <v>45</v>
       </c>
       <c r="C441" s="3">
-        <v>71.930000000000007</v>
+        <v>75.94</v>
       </c>
       <c r="D441" s="6">
-        <v>75.680000000000007</v>
+        <v>80.62</v>
       </c>
       <c r="E441">
         <v>2026</v>
@@ -9939,10 +9935,10 @@
         <v>46</v>
       </c>
       <c r="C442" s="3">
-        <v>19.809999999999999</v>
+        <v>35.92</v>
       </c>
       <c r="D442" s="6">
-        <v>24.53</v>
+        <v>44.47</v>
       </c>
       <c r="E442">
         <v>2026</v>
@@ -9979,10 +9975,10 @@
         <v>48</v>
       </c>
       <c r="C444" s="3">
-        <v>31.74</v>
+        <v>40.049999999999997</v>
       </c>
       <c r="D444" s="6">
-        <v>38.96</v>
+        <v>49.17</v>
       </c>
       <c r="E444">
         <v>2026</v>
@@ -9999,10 +9995,10 @@
         <v>49</v>
       </c>
       <c r="C445" s="3">
-        <v>25.59</v>
+        <v>27.96</v>
       </c>
       <c r="D445" s="6">
-        <v>32.47</v>
+        <v>35.479999999999997</v>
       </c>
       <c r="E445">
         <v>2026</v>
@@ -10019,10 +10015,10 @@
         <v>50</v>
       </c>
       <c r="C446" s="3">
-        <v>26.08</v>
+        <v>26.48</v>
       </c>
       <c r="D446" s="6">
-        <v>33.15</v>
+        <v>33.65</v>
       </c>
       <c r="E446">
         <v>2026</v>
@@ -10059,10 +10055,10 @@
         <v>52</v>
       </c>
       <c r="C448" s="3">
-        <v>25.81</v>
+        <v>34.44</v>
       </c>
       <c r="D448" s="6">
-        <v>31.01</v>
+        <v>41.37</v>
       </c>
       <c r="E448">
         <v>2026</v>
@@ -10079,10 +10075,10 @@
         <v>53</v>
       </c>
       <c r="C449" s="3">
-        <v>17.98</v>
+        <v>29.75</v>
       </c>
       <c r="D449" s="6">
-        <v>22.58</v>
+        <v>37.35</v>
       </c>
       <c r="E449">
         <v>2026</v>
@@ -10139,10 +10135,10 @@
         <v>56</v>
       </c>
       <c r="C452" s="3">
-        <v>51.34</v>
+        <v>52.94</v>
       </c>
       <c r="D452" s="6">
-        <v>55.54</v>
+        <v>57.34</v>
       </c>
       <c r="E452">
         <v>2026</v>
@@ -10159,10 +10155,10 @@
         <v>57</v>
       </c>
       <c r="C453" s="3">
-        <v>40.29</v>
+        <v>59.05</v>
       </c>
       <c r="D453" s="6">
-        <v>47.18</v>
+        <v>70.56</v>
       </c>
       <c r="E453">
         <v>2026</v>
@@ -10179,10 +10175,10 @@
         <v>58</v>
       </c>
       <c r="C454" s="3">
-        <v>32.520000000000003</v>
+        <v>39.69</v>
       </c>
       <c r="D454" s="6">
-        <v>38.33</v>
+        <v>47.14</v>
       </c>
       <c r="E454">
         <v>2026</v>
@@ -10199,10 +10195,10 @@
         <v>59</v>
       </c>
       <c r="C455" s="3">
-        <v>38.979999999999997</v>
+        <v>42.68</v>
       </c>
       <c r="D455" s="6">
-        <v>43.45</v>
+        <v>47.93</v>
       </c>
       <c r="E455">
         <v>2026</v>
@@ -10219,10 +10215,10 @@
         <v>60</v>
       </c>
       <c r="C456" s="3">
-        <v>35.01</v>
+        <v>35.39</v>
       </c>
       <c r="D456" s="6">
-        <v>38.11</v>
+        <v>38.56</v>
       </c>
       <c r="E456">
         <v>2026</v>
@@ -10239,10 +10235,10 @@
         <v>61</v>
       </c>
       <c r="C457" s="3">
-        <v>14.22</v>
+        <v>34.020000000000003</v>
       </c>
       <c r="D457" s="6">
-        <v>17.91</v>
+        <v>42.85</v>
       </c>
       <c r="E457">
         <v>2026</v>
@@ -10259,10 +10255,10 @@
         <v>62</v>
       </c>
       <c r="C458" s="3">
-        <v>15.1</v>
+        <v>31.74</v>
       </c>
       <c r="D458" s="6">
-        <v>18.77</v>
+        <v>39.450000000000003</v>
       </c>
       <c r="E458">
         <v>2026</v>
@@ -10279,10 +10275,10 @@
         <v>63</v>
       </c>
       <c r="C459" s="3">
-        <v>14.37</v>
+        <v>25.11</v>
       </c>
       <c r="D459" s="6">
-        <v>18.14</v>
+        <v>31.7</v>
       </c>
       <c r="E459">
         <v>2026</v>
@@ -10299,10 +10295,10 @@
         <v>64</v>
       </c>
       <c r="C460" s="3">
-        <v>12.39</v>
+        <v>26.88</v>
       </c>
       <c r="D460" s="6">
-        <v>15.59</v>
+        <v>33.799999999999997</v>
       </c>
       <c r="E460">
         <v>2026</v>
@@ -10319,10 +10315,10 @@
         <v>65</v>
       </c>
       <c r="C461" s="3">
-        <v>20.81</v>
+        <v>34.369999999999997</v>
       </c>
       <c r="D461" s="6">
-        <v>25.55</v>
+        <v>42.19</v>
       </c>
       <c r="E461">
         <v>2026</v>
@@ -10339,10 +10335,10 @@
         <v>66</v>
       </c>
       <c r="C462" s="3">
-        <v>24.13</v>
+        <v>26.29</v>
       </c>
       <c r="D462" s="6">
-        <v>30.64</v>
+        <v>33.39</v>
       </c>
       <c r="E462">
         <v>2026</v>
@@ -10359,10 +10355,10 @@
         <v>67</v>
       </c>
       <c r="C463" s="3">
-        <v>16.059999999999999</v>
+        <v>24.07</v>
       </c>
       <c r="D463" s="6">
-        <v>20.09</v>
+        <v>30.1</v>
       </c>
       <c r="E463">
         <v>2026</v>
@@ -10379,10 +10375,10 @@
         <v>68</v>
       </c>
       <c r="C464" s="3">
-        <v>15.09</v>
+        <v>19.3</v>
       </c>
       <c r="D464" s="6">
-        <v>19.18</v>
+        <v>24.54</v>
       </c>
       <c r="E464">
         <v>2026</v>
@@ -10399,10 +10395,10 @@
         <v>69</v>
       </c>
       <c r="C465" s="3">
-        <v>18.62</v>
+        <v>25.51</v>
       </c>
       <c r="D465" s="6">
-        <v>22.93</v>
+        <v>31.4</v>
       </c>
       <c r="E465">
         <v>2026</v>
@@ -10419,10 +10415,10 @@
         <v>70</v>
       </c>
       <c r="C466" s="3">
-        <v>20.51</v>
+        <v>29.01</v>
       </c>
       <c r="D466" s="6">
-        <v>25.25</v>
+        <v>35.72</v>
       </c>
       <c r="E466">
         <v>2026</v>
@@ -10439,10 +10435,10 @@
         <v>71</v>
       </c>
       <c r="C467" s="3">
-        <v>17.489999999999998</v>
+        <v>21.92</v>
       </c>
       <c r="D467" s="6">
-        <v>21.63</v>
+        <v>27.11</v>
       </c>
       <c r="E467">
         <v>2026</v>
@@ -10459,10 +10455,10 @@
         <v>72</v>
       </c>
       <c r="C468" s="3">
-        <v>24.09</v>
+        <v>28.69</v>
       </c>
       <c r="D468" s="6">
-        <v>28.99</v>
+        <v>34.53</v>
       </c>
       <c r="E468">
         <v>2026</v>
@@ -10479,10 +10475,10 @@
         <v>73</v>
       </c>
       <c r="C469" s="3">
-        <v>27.77</v>
+        <v>38.71</v>
       </c>
       <c r="D469" s="6">
-        <v>32.69</v>
+        <v>45.57</v>
       </c>
       <c r="E469">
         <v>2026</v>
@@ -10499,10 +10495,10 @@
         <v>74</v>
       </c>
       <c r="C470" s="3">
-        <v>29.33</v>
+        <v>34.92</v>
       </c>
       <c r="D470" s="6">
-        <v>36.619999999999997</v>
+        <v>43.6</v>
       </c>
       <c r="E470">
         <v>2026</v>
@@ -10519,10 +10515,10 @@
         <v>75</v>
       </c>
       <c r="C471" s="3">
-        <v>25.97</v>
+        <v>30.15</v>
       </c>
       <c r="D471" s="6">
-        <v>31.15</v>
+        <v>36.159999999999997</v>
       </c>
       <c r="E471">
         <v>2026</v>
@@ -10539,10 +10535,10 @@
         <v>76</v>
       </c>
       <c r="C472" s="3">
-        <v>17.16</v>
+        <v>27.99</v>
       </c>
       <c r="D472" s="6">
-        <v>21.57</v>
+        <v>35.19</v>
       </c>
       <c r="E472">
         <v>2026</v>
@@ -10559,10 +10555,10 @@
         <v>77</v>
       </c>
       <c r="C473" s="3">
-        <v>26.61</v>
+        <v>39.020000000000003</v>
       </c>
       <c r="D473" s="6">
-        <v>33.32</v>
+        <v>48.85</v>
       </c>
       <c r="E473">
         <v>2026</v>
@@ -10579,10 +10575,10 @@
         <v>78</v>
       </c>
       <c r="C474" s="3">
-        <v>26.05</v>
+        <v>31.12</v>
       </c>
       <c r="D474" s="6">
-        <v>32.22</v>
+        <v>38.479999999999997</v>
       </c>
       <c r="E474">
         <v>2026</v>
@@ -10599,10 +10595,10 @@
         <v>79</v>
       </c>
       <c r="C475" s="3">
-        <v>21.19</v>
+        <v>24.79</v>
       </c>
       <c r="D475" s="6">
-        <v>26.02</v>
+        <v>30.44</v>
       </c>
       <c r="E475">
         <v>2026</v>
@@ -10619,10 +10615,10 @@
         <v>80</v>
       </c>
       <c r="C476" s="3">
-        <v>28.22</v>
+        <v>37.840000000000003</v>
       </c>
       <c r="D476" s="6">
-        <v>35.04</v>
+        <v>46.97</v>
       </c>
       <c r="E476">
         <v>2026</v>
@@ -10639,10 +10635,10 @@
         <v>81</v>
       </c>
       <c r="C477" s="3">
-        <v>20.02</v>
+        <v>26.18</v>
       </c>
       <c r="D477" s="6">
-        <v>24.63</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="E477">
         <v>2026</v>
@@ -10659,10 +10655,10 @@
         <v>82</v>
       </c>
       <c r="C478" s="3">
-        <v>28.07</v>
+        <v>30.13</v>
       </c>
       <c r="D478" s="6">
-        <v>34.99</v>
+        <v>37.56</v>
       </c>
       <c r="E478">
         <v>2026</v>
@@ -10679,10 +10675,10 @@
         <v>83</v>
       </c>
       <c r="C479" s="3">
-        <v>30.75</v>
+        <v>56.57</v>
       </c>
       <c r="D479" s="6">
-        <v>37.72</v>
+        <v>69.39</v>
       </c>
       <c r="E479">
         <v>2026</v>
@@ -10699,10 +10695,10 @@
         <v>84</v>
       </c>
       <c r="C480" s="3">
-        <v>16.32</v>
+        <v>23.84</v>
       </c>
       <c r="D480" s="6">
-        <v>20.03</v>
+        <v>29.26</v>
       </c>
       <c r="E480">
         <v>2026</v>
@@ -10719,10 +10715,10 @@
         <v>85</v>
       </c>
       <c r="C481" s="3">
-        <v>19.29</v>
+        <v>26.94</v>
       </c>
       <c r="D481" s="6">
-        <v>24.35</v>
+        <v>34.01</v>
       </c>
       <c r="E481">
         <v>2026</v>
@@ -10739,10 +10735,10 @@
         <v>86</v>
       </c>
       <c r="C482" s="3">
-        <v>18.14</v>
+        <v>29.04</v>
       </c>
       <c r="D482" s="6">
-        <v>22.37</v>
+        <v>35.81</v>
       </c>
       <c r="E482">
         <v>2026</v>
@@ -10779,10 +10775,10 @@
         <v>88</v>
       </c>
       <c r="C484" s="3">
-        <v>46.6</v>
+        <v>46.86</v>
       </c>
       <c r="D484" s="6">
-        <v>50.61</v>
+        <v>50.9</v>
       </c>
       <c r="E484">
         <v>2026</v>
@@ -10799,10 +10795,10 @@
         <v>89</v>
       </c>
       <c r="C485" s="3">
-        <v>40.020000000000003</v>
+        <v>41.01</v>
       </c>
       <c r="D485" s="6">
-        <v>44.29</v>
+        <v>45.48</v>
       </c>
       <c r="E485">
         <v>2026</v>
@@ -10839,10 +10835,10 @@
         <v>91</v>
       </c>
       <c r="C487" s="3">
-        <v>38.24</v>
+        <v>38.479999999999997</v>
       </c>
       <c r="D487" s="6">
-        <v>42.53</v>
+        <v>42.81</v>
       </c>
       <c r="E487">
         <v>2026</v>
@@ -10879,10 +10875,10 @@
         <v>93</v>
       </c>
       <c r="C489" s="3">
-        <v>28.85</v>
+        <v>37.869999999999997</v>
       </c>
       <c r="D489" s="6">
-        <v>34.47</v>
+        <v>45.24</v>
       </c>
       <c r="E489">
         <v>2026</v>
@@ -10899,10 +10895,10 @@
         <v>94</v>
       </c>
       <c r="C490" s="3">
-        <v>28.36</v>
+        <v>34.99</v>
       </c>
       <c r="D490" s="6">
-        <v>35.67</v>
+        <v>44.01</v>
       </c>
       <c r="E490">
         <v>2026</v>
@@ -10919,10 +10915,10 @@
         <v>95</v>
       </c>
       <c r="C491" s="3">
-        <v>33.83</v>
+        <v>47.07</v>
       </c>
       <c r="D491" s="6">
-        <v>41.04</v>
+        <v>57.1</v>
       </c>
       <c r="E491">
         <v>2026</v>
@@ -10939,10 +10935,10 @@
         <v>96</v>
       </c>
       <c r="C492" s="3">
-        <v>31.63</v>
+        <v>43.76</v>
       </c>
       <c r="D492" s="6">
-        <v>38.46</v>
+        <v>53.21</v>
       </c>
       <c r="E492">
         <v>2026</v>
@@ -10959,10 +10955,10 @@
         <v>97</v>
       </c>
       <c r="C493" s="3">
-        <v>64.67</v>
+        <v>69.08</v>
       </c>
       <c r="D493" s="6">
-        <v>72.34</v>
+        <v>77.55</v>
       </c>
       <c r="E493">
         <v>2026</v>
@@ -10979,10 +10975,10 @@
         <v>98</v>
       </c>
       <c r="C494" s="3">
-        <v>32.97</v>
+        <v>42.32</v>
       </c>
       <c r="D494" s="6">
-        <v>38.93</v>
+        <v>49.96</v>
       </c>
       <c r="E494">
         <v>2026</v>
@@ -10999,10 +10995,10 @@
         <v>99</v>
       </c>
       <c r="C495" s="3">
-        <v>48.52</v>
+        <v>49.15</v>
       </c>
       <c r="D495" s="6">
-        <v>53.72</v>
+        <v>54.5</v>
       </c>
       <c r="E495">
         <v>2026</v>
@@ -11019,10 +11015,10 @@
         <v>100</v>
       </c>
       <c r="C496" s="3">
-        <v>64.67</v>
+        <v>67.510000000000005</v>
       </c>
       <c r="D496" s="6">
-        <v>71.53</v>
+        <v>74.900000000000006</v>
       </c>
       <c r="E496">
         <v>2026</v>
@@ -11039,10 +11035,10 @@
         <v>101</v>
       </c>
       <c r="C497" s="3">
-        <v>30.79</v>
+        <v>32.54</v>
       </c>
       <c r="D497" s="6">
-        <v>36.79</v>
+        <v>38.880000000000003</v>
       </c>
       <c r="E497">
         <v>2026</v>
@@ -11059,10 +11055,10 @@
         <v>102</v>
       </c>
       <c r="C498" s="3">
-        <v>17.41</v>
+        <v>19.510000000000002</v>
       </c>
       <c r="D498" s="6">
-        <v>21.37</v>
+        <v>23.96</v>
       </c>
       <c r="E498">
         <v>2026</v>
@@ -11079,10 +11075,10 @@
         <v>103</v>
       </c>
       <c r="C499" s="3">
-        <v>51.61</v>
+        <v>52.67</v>
       </c>
       <c r="D499" s="6">
-        <v>56.95</v>
+        <v>58.21</v>
       </c>
       <c r="E499">
         <v>2026</v>
@@ -11099,10 +11095,10 @@
         <v>104</v>
       </c>
       <c r="C500" s="3">
-        <v>41.89</v>
+        <v>46</v>
       </c>
       <c r="D500" s="6">
-        <v>46.03</v>
+        <v>50.68</v>
       </c>
       <c r="E500">
         <v>2026</v>
@@ -11119,10 +11115,10 @@
         <v>105</v>
       </c>
       <c r="C501" s="3">
-        <v>46.29</v>
+        <v>49.86</v>
       </c>
       <c r="D501" s="6">
-        <v>50.88</v>
+        <v>55.06</v>
       </c>
       <c r="E501">
         <v>2026</v>
@@ -11159,10 +11155,10 @@
         <v>107</v>
       </c>
       <c r="C503" s="3">
-        <v>22.07</v>
+        <v>30.22</v>
       </c>
       <c r="D503" s="6">
-        <v>28</v>
+        <v>38.33</v>
       </c>
       <c r="E503">
         <v>2026</v>
@@ -11179,10 +11175,10 @@
         <v>108</v>
       </c>
       <c r="C504" s="3">
-        <v>36.869999999999997</v>
+        <v>38.549999999999997</v>
       </c>
       <c r="D504" s="6">
-        <v>42.02</v>
+        <v>44</v>
       </c>
       <c r="E504">
         <v>2026</v>
@@ -11199,10 +11195,10 @@
         <v>109</v>
       </c>
       <c r="C505" s="3">
-        <v>50.26</v>
+        <v>52.45</v>
       </c>
       <c r="D505" s="6">
-        <v>55.33</v>
+        <v>57.83</v>
       </c>
       <c r="E505">
         <v>2026</v>
@@ -11219,10 +11215,10 @@
         <v>110</v>
       </c>
       <c r="C506" s="3">
-        <v>44.19</v>
+        <v>58.61</v>
       </c>
       <c r="D506" s="6">
-        <v>50.62</v>
+        <v>67.150000000000006</v>
       </c>
       <c r="E506">
         <v>2026</v>
@@ -11239,10 +11235,10 @@
         <v>111</v>
       </c>
       <c r="C507" s="3">
-        <v>48.64</v>
+        <v>49.4</v>
       </c>
       <c r="D507" s="6">
-        <v>54.4</v>
+        <v>55.29</v>
       </c>
       <c r="E507">
         <v>2026</v>
@@ -11279,10 +11275,10 @@
         <v>113</v>
       </c>
       <c r="C509" s="3">
-        <v>46.57</v>
+        <v>50.99</v>
       </c>
       <c r="D509" s="6">
-        <v>53.71</v>
+        <v>59.26</v>
       </c>
       <c r="E509">
         <v>2026</v>
@@ -11299,10 +11295,10 @@
         <v>114</v>
       </c>
       <c r="C510" s="3">
-        <v>67.7</v>
+        <v>68.599999999999994</v>
       </c>
       <c r="D510" s="6">
-        <v>75.77</v>
+        <v>76.87</v>
       </c>
       <c r="E510">
         <v>2026</v>
@@ -11319,10 +11315,10 @@
         <v>115</v>
       </c>
       <c r="C511" s="3">
-        <v>45.38</v>
+        <v>62.5</v>
       </c>
       <c r="D511" s="6">
-        <v>54.7</v>
+        <v>75.34</v>
       </c>
       <c r="E511">
         <v>2026</v>
@@ -11339,10 +11335,10 @@
         <v>116</v>
       </c>
       <c r="C512" s="3">
-        <v>29.36</v>
+        <v>30.3</v>
       </c>
       <c r="D512" s="6">
-        <v>33.21</v>
+        <v>34.32</v>
       </c>
       <c r="E512">
         <v>2026</v>
@@ -11359,10 +11355,10 @@
         <v>117</v>
       </c>
       <c r="C513" s="3">
-        <v>43.12</v>
+        <v>55.85</v>
       </c>
       <c r="D513" s="6">
-        <v>52.51</v>
+        <v>68</v>
       </c>
       <c r="E513">
         <v>2026</v>
@@ -11379,10 +11375,10 @@
         <v>118</v>
       </c>
       <c r="C514" s="3">
-        <v>64.349999999999994</v>
+        <v>67.95</v>
       </c>
       <c r="D514" s="6">
-        <v>70.459999999999994</v>
+        <v>74.56</v>
       </c>
       <c r="E514">
         <v>2026</v>
@@ -11399,10 +11395,10 @@
         <v>119</v>
       </c>
       <c r="C515" s="3">
-        <v>28.07</v>
+        <v>28.31</v>
       </c>
       <c r="D515" s="6">
-        <v>31.67</v>
+        <v>31.96</v>
       </c>
       <c r="E515">
         <v>2026</v>
@@ -11419,10 +11415,10 @@
         <v>120</v>
       </c>
       <c r="C516" s="3">
-        <v>32.869999999999997</v>
+        <v>33.9</v>
       </c>
       <c r="D516" s="6">
-        <v>36.33</v>
+        <v>37.58</v>
       </c>
       <c r="E516">
         <v>2026</v>
@@ -11439,10 +11435,10 @@
         <v>121</v>
       </c>
       <c r="C517" s="3">
-        <v>32.22</v>
+        <v>33.299999999999997</v>
       </c>
       <c r="D517" s="6">
-        <v>35.39</v>
+        <v>36.68</v>
       </c>
       <c r="E517">
         <v>2026</v>
@@ -11459,10 +11455,10 @@
         <v>122</v>
       </c>
       <c r="C518" s="3">
-        <v>54.24</v>
+        <v>61.18</v>
       </c>
       <c r="D518" s="6">
-        <v>60.92</v>
+        <v>69.42</v>
       </c>
       <c r="E518">
         <v>2026</v>
@@ -11479,10 +11475,10 @@
         <v>123</v>
       </c>
       <c r="C519" s="3">
-        <v>37.25</v>
+        <v>37.64</v>
       </c>
       <c r="D519" s="6">
-        <v>40.44</v>
+        <v>40.89</v>
       </c>
       <c r="E519">
         <v>2026</v>
@@ -11499,10 +11495,10 @@
         <v>124</v>
       </c>
       <c r="C520" s="3">
-        <v>101.53</v>
+        <v>109.25</v>
       </c>
       <c r="D520" s="6">
-        <v>106.7</v>
+        <v>115.8</v>
       </c>
       <c r="E520">
         <v>2026</v>
@@ -11519,10 +11515,10 @@
         <v>125</v>
       </c>
       <c r="C521" s="3">
-        <v>17.739999999999998</v>
+        <v>24.04</v>
       </c>
       <c r="D521" s="6">
-        <v>21.94</v>
+        <v>29.74</v>
       </c>
       <c r="E521">
         <v>2026</v>
@@ -11539,10 +11535,10 @@
         <v>126</v>
       </c>
       <c r="C522" s="3">
-        <v>18.14</v>
+        <v>23.24</v>
       </c>
       <c r="D522" s="6">
-        <v>22.24</v>
+        <v>28.5</v>
       </c>
       <c r="E522">
         <v>2026</v>
@@ -11559,10 +11555,10 @@
         <v>127</v>
       </c>
       <c r="C523" s="3">
-        <v>19.23</v>
+        <v>27.54</v>
       </c>
       <c r="D523" s="6">
-        <v>23.72</v>
+        <v>33.97</v>
       </c>
       <c r="E523">
         <v>2026</v>
@@ -11579,10 +11575,10 @@
         <v>128</v>
       </c>
       <c r="C524" s="3">
-        <v>22.2</v>
+        <v>28.94</v>
       </c>
       <c r="D524" s="6">
-        <v>27.08</v>
+        <v>35.299999999999997</v>
       </c>
       <c r="E524">
         <v>2026</v>
@@ -11599,10 +11595,10 @@
         <v>129</v>
       </c>
       <c r="C525" s="3">
-        <v>38.450000000000003</v>
+        <v>43.02</v>
       </c>
       <c r="D525" s="6">
-        <v>45.2</v>
+        <v>50.57</v>
       </c>
       <c r="E525">
         <v>2026</v>
@@ -11619,10 +11615,10 @@
         <v>130</v>
       </c>
       <c r="C526" s="3">
-        <v>25.7</v>
+        <v>38.9</v>
       </c>
       <c r="D526" s="6">
-        <v>30.96</v>
+        <v>46.87</v>
       </c>
       <c r="E526">
         <v>2026</v>
@@ -11639,10 +11635,10 @@
         <v>131</v>
       </c>
       <c r="C527" s="3">
-        <v>22.63</v>
+        <v>31.79</v>
       </c>
       <c r="D527" s="6">
-        <v>27.34</v>
+        <v>38.4</v>
       </c>
       <c r="E527">
         <v>2026</v>
@@ -11659,10 +11655,10 @@
         <v>132</v>
       </c>
       <c r="C528" s="3">
-        <v>30.12</v>
+        <v>36.24</v>
       </c>
       <c r="D528" s="6">
-        <v>35.770000000000003</v>
+        <v>43.04</v>
       </c>
       <c r="E528">
         <v>2026</v>
@@ -11679,10 +11675,10 @@
         <v>133</v>
       </c>
       <c r="C529" s="3">
-        <v>22.09</v>
+        <v>29.61</v>
       </c>
       <c r="D529" s="6">
-        <v>27.26</v>
+        <v>36.54</v>
       </c>
       <c r="E529">
         <v>2026</v>
@@ -11699,10 +11695,10 @@
         <v>134</v>
       </c>
       <c r="C530" s="3">
-        <v>5.74</v>
+        <v>54.85</v>
       </c>
       <c r="D530" s="6">
-        <v>7.32</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="E530">
         <v>2026</v>
@@ -11719,10 +11715,10 @@
         <v>135</v>
       </c>
       <c r="C531" s="3">
-        <v>31.09</v>
+        <v>37.71</v>
       </c>
       <c r="D531" s="6">
-        <v>36.909999999999997</v>
+        <v>44.77</v>
       </c>
       <c r="E531">
         <v>2026</v>
@@ -11739,10 +11735,10 @@
         <v>136</v>
       </c>
       <c r="C532" s="3">
-        <v>20.41</v>
+        <v>30.77</v>
       </c>
       <c r="D532" s="6">
-        <v>25.4</v>
+        <v>38.299999999999997</v>
       </c>
       <c r="E532">
         <v>2026</v>
@@ -11759,10 +11755,10 @@
         <v>137</v>
       </c>
       <c r="C533" s="3">
-        <v>66.209999999999994</v>
+        <v>69.430000000000007</v>
       </c>
       <c r="D533" s="6">
-        <v>71.680000000000007</v>
+        <v>75.510000000000005</v>
       </c>
       <c r="E533">
         <v>2026</v>
@@ -11779,10 +11775,10 @@
         <v>138</v>
       </c>
       <c r="C534" s="3">
-        <v>33.51</v>
+        <v>37.07</v>
       </c>
       <c r="D534" s="6">
-        <v>37.69</v>
+        <v>41.87</v>
       </c>
       <c r="E534">
         <v>2026</v>
@@ -11799,10 +11795,10 @@
         <v>139</v>
       </c>
       <c r="C535" s="3">
-        <v>35.020000000000003</v>
+        <v>42.02</v>
       </c>
       <c r="D535" s="6">
-        <v>41.07</v>
+        <v>49.27</v>
       </c>
       <c r="E535">
         <v>2026</v>
@@ -11819,10 +11815,10 @@
         <v>140</v>
       </c>
       <c r="C536" s="3">
-        <v>13.96</v>
+        <v>15.57</v>
       </c>
       <c r="D536" s="6">
-        <v>17.18</v>
+        <v>19.16</v>
       </c>
       <c r="E536">
         <v>2026</v>
@@ -11839,10 +11835,10 @@
         <v>141</v>
       </c>
       <c r="C537" s="3">
-        <v>13.22</v>
+        <v>15.26</v>
       </c>
       <c r="D537" s="6">
-        <v>15.89</v>
+        <v>18.34</v>
       </c>
       <c r="E537">
         <v>2026</v>
@@ -11859,10 +11855,10 @@
         <v>142</v>
       </c>
       <c r="C538" s="3">
-        <v>22.3</v>
+        <v>35.5</v>
       </c>
       <c r="D538" s="6">
-        <v>27.85</v>
+        <v>44.34</v>
       </c>
       <c r="E538">
         <v>2026</v>
@@ -11879,10 +11875,10 @@
         <v>143</v>
       </c>
       <c r="C539" s="3">
-        <v>29.7</v>
+        <v>48.35</v>
       </c>
       <c r="D539" s="6">
-        <v>37.86</v>
+        <v>61.63</v>
       </c>
       <c r="E539">
         <v>2026</v>
@@ -11899,10 +11895,10 @@
         <v>144</v>
       </c>
       <c r="C540" s="3">
-        <v>14.76</v>
+        <v>28.38</v>
       </c>
       <c r="D540" s="6">
-        <v>18.36</v>
+        <v>35.299999999999997</v>
       </c>
       <c r="E540">
         <v>2026</v>
@@ -11919,10 +11915,10 @@
         <v>145</v>
       </c>
       <c r="C541" s="3">
-        <v>21.06</v>
+        <v>37.590000000000003</v>
       </c>
       <c r="D541" s="6">
-        <v>26.19</v>
+        <v>46.75</v>
       </c>
       <c r="E541">
         <v>2026</v>
@@ -11939,10 +11935,10 @@
         <v>146</v>
       </c>
       <c r="C542" s="3">
-        <v>17.5</v>
+        <v>32.840000000000003</v>
       </c>
       <c r="D542" s="6">
-        <v>22.23</v>
+        <v>41.72</v>
       </c>
       <c r="E542">
         <v>2026</v>
@@ -11959,10 +11955,10 @@
         <v>147</v>
       </c>
       <c r="C543" s="3">
-        <v>17.670000000000002</v>
+        <v>28.27</v>
       </c>
       <c r="D543" s="6">
-        <v>21.71</v>
+        <v>34.74</v>
       </c>
       <c r="E543">
         <v>2026</v>
@@ -11979,10 +11975,10 @@
         <v>148</v>
       </c>
       <c r="C544" s="3">
-        <v>17.53</v>
+        <v>20.94</v>
       </c>
       <c r="D544" s="6">
-        <v>20.84</v>
+        <v>24.89</v>
       </c>
       <c r="E544">
         <v>2026</v>
@@ -11999,10 +11995,10 @@
         <v>149</v>
       </c>
       <c r="C545" s="3">
-        <v>28.49</v>
+        <v>34.630000000000003</v>
       </c>
       <c r="D545" s="6">
-        <v>33.97</v>
+        <v>41.3</v>
       </c>
       <c r="E545">
         <v>2026</v>
@@ -12019,10 +12015,10 @@
         <v>150</v>
       </c>
       <c r="C546" s="3">
-        <v>22.15</v>
+        <v>24.7</v>
       </c>
       <c r="D546" s="6">
-        <v>26.72</v>
+        <v>29.8</v>
       </c>
       <c r="E546">
         <v>2026</v>
@@ -12039,10 +12035,10 @@
         <v>151</v>
       </c>
       <c r="C547" s="3">
-        <v>21.48</v>
+        <v>22.82</v>
       </c>
       <c r="D547" s="6">
-        <v>24.61</v>
+        <v>26.14</v>
       </c>
       <c r="E547">
         <v>2026</v>
@@ -12059,10 +12055,10 @@
         <v>152</v>
       </c>
       <c r="C548" s="3">
-        <v>24.12</v>
+        <v>29.52</v>
       </c>
       <c r="D548" s="6">
-        <v>29.42</v>
+        <v>36</v>
       </c>
       <c r="E548">
         <v>2026</v>
@@ -12079,10 +12075,10 @@
         <v>153</v>
       </c>
       <c r="C549" s="3">
-        <v>19.16</v>
+        <v>26.96</v>
       </c>
       <c r="D549" s="6">
-        <v>24.04</v>
+        <v>33.83</v>
       </c>
       <c r="E549">
         <v>2026</v>
@@ -12099,10 +12095,10 @@
         <v>154</v>
       </c>
       <c r="C550" s="3">
-        <v>11.11</v>
+        <v>14.62</v>
       </c>
       <c r="D550" s="6">
-        <v>14.08</v>
+        <v>18.53</v>
       </c>
       <c r="E550">
         <v>2026</v>
@@ -12119,10 +12115,10 @@
         <v>155</v>
       </c>
       <c r="C551" s="3">
-        <v>12.35</v>
+        <v>12.38</v>
       </c>
       <c r="D551" s="6">
-        <v>14.83</v>
+        <v>14.87</v>
       </c>
       <c r="E551">
         <v>2026</v>
@@ -12199,10 +12195,10 @@
         <v>159</v>
       </c>
       <c r="C555" s="3">
-        <v>14.34</v>
+        <v>15.45</v>
       </c>
       <c r="D555" s="6">
-        <v>17.38</v>
+        <v>18.72</v>
       </c>
       <c r="E555">
         <v>2026</v>
@@ -12219,10 +12215,10 @@
         <v>160</v>
       </c>
       <c r="C556" s="3">
-        <v>22.24</v>
+        <v>28.76</v>
       </c>
       <c r="D556" s="6">
-        <v>27.41</v>
+        <v>35.44</v>
       </c>
       <c r="E556">
         <v>2026</v>
@@ -12239,10 +12235,10 @@
         <v>161</v>
       </c>
       <c r="C557" s="3">
-        <v>14.91</v>
+        <v>19.34</v>
       </c>
       <c r="D557" s="6">
-        <v>18.899999999999999</v>
+        <v>24.52</v>
       </c>
       <c r="E557">
         <v>2026</v>
@@ -12259,10 +12255,10 @@
         <v>162</v>
       </c>
       <c r="C558" s="3">
-        <v>31.16</v>
+        <v>31.55</v>
       </c>
       <c r="D558" s="6">
-        <v>34.94</v>
+        <v>35.43</v>
       </c>
       <c r="E558">
         <v>2026</v>
@@ -12279,10 +12275,10 @@
         <v>163</v>
       </c>
       <c r="C559" s="3">
-        <v>28.83</v>
+        <v>44.61</v>
       </c>
       <c r="D559" s="6">
-        <v>36.479999999999997</v>
+        <v>56.46</v>
       </c>
       <c r="E559">
         <v>2026</v>
@@ -12299,10 +12295,10 @@
         <v>164</v>
       </c>
       <c r="C560" s="3">
-        <v>28.01</v>
+        <v>43.41</v>
       </c>
       <c r="D560" s="6">
-        <v>35.17</v>
+        <v>54.51</v>
       </c>
       <c r="E560">
         <v>2026</v>
@@ -12319,10 +12315,10 @@
         <v>165</v>
       </c>
       <c r="C561" s="3">
-        <v>23.18</v>
+        <v>27.82</v>
       </c>
       <c r="D561" s="6">
-        <v>28.26</v>
+        <v>33.909999999999997</v>
       </c>
       <c r="E561">
         <v>2026</v>
@@ -12339,10 +12335,10 @@
         <v>166</v>
       </c>
       <c r="C562" s="3">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D562" s="6">
-        <v>36.950000000000003</v>
+        <v>41.87</v>
       </c>
       <c r="E562">
         <v>2026</v>
@@ -12359,10 +12355,10 @@
         <v>167</v>
       </c>
       <c r="C563" s="3">
-        <v>20.3</v>
+        <v>24.25</v>
       </c>
       <c r="D563" s="6">
-        <v>24.52</v>
+        <v>29.29</v>
       </c>
       <c r="E563">
         <v>2026</v>
@@ -12379,10 +12375,10 @@
         <v>168</v>
       </c>
       <c r="C564" s="3">
-        <v>23.69</v>
+        <v>27.31</v>
       </c>
       <c r="D564" s="6">
-        <v>29.38</v>
+        <v>33.880000000000003</v>
       </c>
       <c r="E564">
         <v>2026</v>
@@ -12399,10 +12395,10 @@
         <v>169</v>
       </c>
       <c r="C565" s="3">
-        <v>27.5</v>
+        <v>42.8</v>
       </c>
       <c r="D565" s="6">
-        <v>33.369999999999997</v>
+        <v>51.93</v>
       </c>
       <c r="E565">
         <v>2026</v>
@@ -12419,10 +12415,10 @@
         <v>170</v>
       </c>
       <c r="C566" s="3">
-        <v>31.15</v>
+        <v>34.31</v>
       </c>
       <c r="D566" s="6">
-        <v>39.68</v>
+        <v>43.7</v>
       </c>
       <c r="E566">
         <v>2026</v>
@@ -12439,10 +12435,10 @@
         <v>171</v>
       </c>
       <c r="C567" s="3">
-        <v>12.61</v>
+        <v>21.38</v>
       </c>
       <c r="D567" s="6">
-        <v>15.82</v>
+        <v>26.82</v>
       </c>
       <c r="E567">
         <v>2026</v>
@@ -12459,10 +12455,10 @@
         <v>172</v>
       </c>
       <c r="C568" s="3">
-        <v>13.98</v>
+        <v>20.2</v>
       </c>
       <c r="D568" s="6">
-        <v>17.22</v>
+        <v>24.89</v>
       </c>
       <c r="E568">
         <v>2026</v>
@@ -12479,10 +12475,10 @@
         <v>173</v>
       </c>
       <c r="C569" s="3">
-        <v>15.18</v>
+        <v>21.73</v>
       </c>
       <c r="D569" s="6">
-        <v>18.82</v>
+        <v>26.94</v>
       </c>
       <c r="E569">
         <v>2026</v>
@@ -12499,10 +12495,10 @@
         <v>174</v>
       </c>
       <c r="C570" s="3">
-        <v>13.46</v>
+        <v>17.66</v>
       </c>
       <c r="D570" s="6">
-        <v>16.98</v>
+        <v>22.27</v>
       </c>
       <c r="E570">
         <v>2026</v>
@@ -12519,10 +12515,10 @@
         <v>175</v>
       </c>
       <c r="C571" s="3">
-        <v>11.55</v>
+        <v>20.79</v>
       </c>
       <c r="D571" s="6">
-        <v>14.6</v>
+        <v>26.26</v>
       </c>
       <c r="E571">
         <v>2026</v>
@@ -12539,10 +12535,10 @@
         <v>176</v>
       </c>
       <c r="C572" s="3">
-        <v>12.98</v>
+        <v>16.59</v>
       </c>
       <c r="D572" s="6">
-        <v>16.38</v>
+        <v>20.93</v>
       </c>
       <c r="E572">
         <v>2026</v>
@@ -12559,10 +12555,10 @@
         <v>177</v>
       </c>
       <c r="C573" s="3">
-        <v>26.37</v>
+        <v>32.01</v>
       </c>
       <c r="D573" s="6">
-        <v>32.86</v>
+        <v>39.9</v>
       </c>
       <c r="E573">
         <v>2026</v>
@@ -12579,10 +12575,10 @@
         <v>178</v>
       </c>
       <c r="C574" s="3">
-        <v>26.26</v>
+        <v>37.83</v>
       </c>
       <c r="D574" s="6">
-        <v>32.479999999999997</v>
+        <v>46.79</v>
       </c>
       <c r="E574">
         <v>2026</v>
@@ -12599,10 +12595,10 @@
         <v>179</v>
       </c>
       <c r="C575" s="3">
-        <v>30.06</v>
+        <v>39.340000000000003</v>
       </c>
       <c r="D575" s="6">
-        <v>35.53</v>
+        <v>46.51</v>
       </c>
       <c r="E575">
         <v>2026</v>
@@ -12619,10 +12615,10 @@
         <v>180</v>
       </c>
       <c r="C576" s="3">
-        <v>17.940000000000001</v>
+        <v>48.64</v>
       </c>
       <c r="D576" s="6">
-        <v>22.91</v>
+        <v>62.13</v>
       </c>
       <c r="E576">
         <v>2026</v>
@@ -12639,10 +12635,10 @@
         <v>181</v>
       </c>
       <c r="C577" s="3">
-        <v>25.66</v>
+        <v>45.87</v>
       </c>
       <c r="D577" s="6">
-        <v>32.770000000000003</v>
+        <v>58.56</v>
       </c>
       <c r="E577">
         <v>2026</v>
@@ -12659,10 +12655,10 @@
         <v>182</v>
       </c>
       <c r="C578" s="3">
-        <v>41.9</v>
+        <v>44.13</v>
       </c>
       <c r="D578" s="6">
-        <v>47.8</v>
+        <v>50.54</v>
       </c>
       <c r="E578">
         <v>2026</v>
@@ -12679,10 +12675,10 @@
         <v>183</v>
       </c>
       <c r="C579" s="3">
-        <v>26.12</v>
+        <v>41.87</v>
       </c>
       <c r="D579" s="6">
-        <v>32.51</v>
+        <v>52.11</v>
       </c>
       <c r="E579">
         <v>2026</v>
@@ -12699,10 +12695,10 @@
         <v>184</v>
       </c>
       <c r="C580" s="3">
-        <v>27.68</v>
+        <v>45.89</v>
       </c>
       <c r="D580" s="6">
-        <v>34.83</v>
+        <v>57.74</v>
       </c>
       <c r="E580">
         <v>2026</v>
@@ -12719,10 +12715,10 @@
         <v>185</v>
       </c>
       <c r="C581" s="3">
-        <v>32.17</v>
+        <v>35.869999999999997</v>
       </c>
       <c r="D581" s="6">
-        <v>37.64</v>
+        <v>41.97</v>
       </c>
       <c r="E581">
         <v>2026</v>
@@ -12739,10 +12735,10 @@
         <v>186</v>
       </c>
       <c r="C582" s="3">
-        <v>64.650000000000006</v>
+        <v>69.91</v>
       </c>
       <c r="D582" s="6">
-        <v>72.75</v>
+        <v>79.209999999999994</v>
       </c>
       <c r="E582">
         <v>2026</v>
@@ -12759,10 +12755,10 @@
         <v>187</v>
       </c>
       <c r="C583" s="3">
-        <v>49.41</v>
+        <v>55.79</v>
       </c>
       <c r="D583" s="6">
-        <v>55.19</v>
+        <v>62.66</v>
       </c>
       <c r="E583">
         <v>2026</v>
@@ -12779,10 +12775,10 @@
         <v>188</v>
       </c>
       <c r="C584" s="3">
-        <v>34.299999999999997</v>
+        <v>41.95</v>
       </c>
       <c r="D584" s="6">
-        <v>42.1</v>
+        <v>51.49</v>
       </c>
       <c r="E584">
         <v>2026</v>
@@ -12799,10 +12795,10 @@
         <v>189</v>
       </c>
       <c r="C585" s="3">
-        <v>128.19</v>
+        <v>128.18</v>
       </c>
       <c r="D585" s="6">
-        <v>165.79</v>
+        <v>165.78</v>
       </c>
       <c r="E585">
         <v>2026</v>
@@ -12819,10 +12815,10 @@
         <v>190</v>
       </c>
       <c r="C586" s="3">
-        <v>19.53</v>
+        <v>34.299999999999997</v>
       </c>
       <c r="D586" s="6">
-        <v>23.91</v>
+        <v>42</v>
       </c>
       <c r="E586">
         <v>2026</v>
@@ -12839,10 +12835,10 @@
         <v>191</v>
       </c>
       <c r="C587" s="3">
-        <v>20.14</v>
+        <v>24.23</v>
       </c>
       <c r="D587" s="6">
-        <v>24.99</v>
+        <v>30.06</v>
       </c>
       <c r="E587">
         <v>2026</v>
@@ -12859,10 +12855,10 @@
         <v>192</v>
       </c>
       <c r="C588" s="3">
-        <v>17.87</v>
+        <v>21.14</v>
       </c>
       <c r="D588" s="6">
-        <v>22.64</v>
+        <v>26.77</v>
       </c>
       <c r="E588">
         <v>2026</v>
@@ -12879,10 +12875,10 @@
         <v>193</v>
       </c>
       <c r="C589" s="3">
-        <v>25.04</v>
+        <v>32.75</v>
       </c>
       <c r="D589" s="6">
-        <v>29.56</v>
+        <v>38.67</v>
       </c>
       <c r="E589">
         <v>2026</v>
@@ -12899,10 +12895,10 @@
         <v>194</v>
       </c>
       <c r="C590" s="3">
-        <v>34.06</v>
+        <v>34.31</v>
       </c>
       <c r="D590" s="6">
-        <v>37.42</v>
+        <v>37.700000000000003</v>
       </c>
       <c r="E590">
         <v>2026</v>
@@ -12919,10 +12915,10 @@
         <v>195</v>
       </c>
       <c r="C591" s="3">
-        <v>15.23</v>
+        <v>30.81</v>
       </c>
       <c r="D591" s="6">
-        <v>19.14</v>
+        <v>38.71</v>
       </c>
       <c r="E591">
         <v>2026</v>
@@ -12939,10 +12935,10 @@
         <v>196</v>
       </c>
       <c r="C592" s="3">
-        <v>15.88</v>
+        <v>36.61</v>
       </c>
       <c r="D592" s="6">
-        <v>19.98</v>
+        <v>46.06</v>
       </c>
       <c r="E592">
         <v>2026</v>
@@ -12959,10 +12955,10 @@
         <v>197</v>
       </c>
       <c r="C593" s="3">
-        <v>39.89</v>
+        <v>41.03</v>
       </c>
       <c r="D593" s="6">
-        <v>44.65</v>
+        <v>46.02</v>
       </c>
       <c r="E593">
         <v>2026</v>
@@ -12979,10 +12975,10 @@
         <v>198</v>
       </c>
       <c r="C594" s="3">
-        <v>23.05</v>
+        <v>23.85</v>
       </c>
       <c r="D594" s="6">
-        <v>26.89</v>
+        <v>27.89</v>
       </c>
       <c r="E594">
         <v>2026</v>
@@ -12999,10 +12995,10 @@
         <v>199</v>
       </c>
       <c r="C595" s="3">
-        <v>13.72</v>
+        <v>16.579999999999998</v>
       </c>
       <c r="D595" s="6">
-        <v>17.2</v>
+        <v>20.8</v>
       </c>
       <c r="E595">
         <v>2026</v>
@@ -13019,10 +13015,10 @@
         <v>200</v>
       </c>
       <c r="C596" s="3">
-        <v>39.32</v>
+        <v>42.15</v>
       </c>
       <c r="D596" s="6">
-        <v>44.11</v>
+        <v>47.49</v>
       </c>
       <c r="E596">
         <v>2026</v>
@@ -13039,10 +13035,10 @@
         <v>201</v>
       </c>
       <c r="C597" s="3">
-        <v>15.84</v>
+        <v>22.64</v>
       </c>
       <c r="D597" s="6">
-        <v>19.64</v>
+        <v>28.07</v>
       </c>
       <c r="E597">
         <v>2026</v>
@@ -13059,10 +13055,10 @@
         <v>202</v>
       </c>
       <c r="C598" s="3">
-        <v>20.81</v>
+        <v>31.8</v>
       </c>
       <c r="D598" s="6">
-        <v>25.09</v>
+        <v>38.33</v>
       </c>
       <c r="E598">
         <v>2026</v>
@@ -13079,10 +13075,10 @@
         <v>203</v>
       </c>
       <c r="C599" s="3">
-        <v>32</v>
+        <v>33.92</v>
       </c>
       <c r="D599" s="6">
-        <v>35.61</v>
+        <v>37.82</v>
       </c>
       <c r="E599">
         <v>2026</v>
@@ -13099,10 +13095,10 @@
         <v>204</v>
       </c>
       <c r="C600" s="3">
-        <v>22.13</v>
+        <v>22.94</v>
       </c>
       <c r="D600" s="6">
-        <v>25.69</v>
+        <v>26.69</v>
       </c>
       <c r="E600">
         <v>2026</v>
@@ -13119,10 +13115,10 @@
         <v>202</v>
       </c>
       <c r="C601" s="3">
-        <v>20.81</v>
+        <v>31.8</v>
       </c>
       <c r="D601" s="6">
-        <v>25.09</v>
+        <v>38.33</v>
       </c>
       <c r="E601">
         <v>2026</v>
